--- a/基本設計/03_画面共通設計書.xlsx
+++ b/基本設計/03_画面共通設計書.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rd17a5067d1b24f61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rde651ed277194a8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_画面一覧" sheetId="13" r:id="R1e750fc252274bf6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_画面遷移" sheetId="14" r:id="Rf4543a2a86a146c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_共通レイアウト" sheetId="15" r:id="R23c1e2d3020b4f4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_入力チェック" sheetId="17" r:id="R0766439565b34c94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_WF作成規約" sheetId="18" r:id="R8a85bcc55fac4d7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_共通API呼出" sheetId="19" r:id="R7913c05d03824246"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R7cdbb3e33d7b4385"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R0f279ef6a9db4709"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_画面一覧" sheetId="13" r:id="R03d613a020d14796"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_画面遷移" sheetId="14" r:id="R67a0a16eb9dc4a5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_共通レイアウト" sheetId="15" r:id="R9a86fe38bf0b497a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_入力チェック" sheetId="17" r:id="R2ce3d4f8f19c4cbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_WF作成規約" sheetId="18" r:id="Rf51b82f4d3d249fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_共通API呼出" sheetId="19" r:id="R9f7ea9abe16e4891"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1518,10 +1518,7 @@
       <x:c r="F16" s="259"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.8 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
+      <x:c r="A17"/>
       <x:c r="C17"/>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -1537,25 +1534,22 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" s="302" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.7 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
-      <x:c r="C19" s="302"/>
-      <x:c r="D19" s="302"/>
-      <x:c r="E19" s="302"/>
-      <x:c r="F19" s="302"/>
-      <x:c r="G19" s="302"/>
-      <x:c r="H19" s="302"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="302"/>
-      <x:c r="C20" s="302"/>
-      <x:c r="D20" s="302"/>
-      <x:c r="E20" s="302"/>
-      <x:c r="F20" s="302"/>
-      <x:c r="G20" s="302"/>
-      <x:c r="H20" s="302"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="302"/>

--- a/基本設計/03_画面共通設計書.xlsx
+++ b/基本設計/03_画面共通設計書.xlsx
@@ -2,14 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R7cdbb3e33d7b4385"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R0f279ef6a9db4709"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_画面一覧" sheetId="13" r:id="R03d613a020d14796"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_画面遷移" sheetId="14" r:id="R67a0a16eb9dc4a5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_共通レイアウト" sheetId="15" r:id="R9a86fe38bf0b497a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_入力チェック" sheetId="17" r:id="R2ce3d4f8f19c4cbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_WF作成規約" sheetId="18" r:id="Rf51b82f4d3d249fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_共通API呼出" sheetId="19" r:id="R9f7ea9abe16e4891"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rb47faf818a7e433f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R36f2176cc9264ed7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_画面一覧" sheetId="13" r:id="R45fcae201dfc4e0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_画面遷移" sheetId="14" r:id="Ra9bfd8434a684b07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_共通レイアウト" sheetId="15" r:id="R4cfe3c3914764d9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_入力チェック" sheetId="17" r:id="R86c9ce915cba4d3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_WF作成規約" sheetId="18" r:id="R34dc80adccef4155"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_共通API呼出" sheetId="19" r:id="R1cb30ceb50744285"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_画面Route定義" sheetId="20" r:id="R1055079642f5481d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_ValidationLifecycle" sheetId="21" r:id="R858d348e80c84ef7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_共通例外遷移" sheetId="22" r:id="Rdadebf942b314834"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23,7 +26,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="32">
+  <x:fonts count="38">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -203,8 +206,41 @@
       <x:color rgb="FF1F1F1F"/>
       <x:name val="Yu Gothic"/>
     </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF333333"/>
+      <x:name val="Meiryo"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF333333"/>
+      <x:name val="Meiryo"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Meiryo"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF18283A"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="17"/>
+      <x:color rgb="FF193C61"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="34">
+  <x:fills count="42">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -371,8 +407,48 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF234F77"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF1F5FA"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="11">
+  <x:borders count="15">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -454,11 +530,67 @@
         <x:color rgb="FF8EA9C1"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF9FBAD0"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF9FBAD0"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF9FBAD0"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF9FBAD0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF1F4E78"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF1F4E78"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF1F4E78"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF1F4E78"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB7C9D6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFB7C9D6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFB7C9D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB7C9D6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="303">
+  <x:cellXfs count="365">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1088,6 +1220,148 @@
     <x:xf numFmtId="0" fontId="31" fillId="33" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="32" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="33" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="35" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="36" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="34" fillId="34" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="34" fillId="34" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="34" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="34" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="34" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="34" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="34" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="32" fillId="36" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="32" fillId="36" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="36" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="37" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="32" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="32" fillId="38" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="32" fillId="38" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="38" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="32" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="32" fillId="37" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="32" fillId="37" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="39" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="35" fillId="39" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="35" fillId="39" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="30" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="36" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="36" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="36" fillId="41" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="33" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1386,7 +1660,36 @@
     <x:col min="26" max="26" width="3" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1"/>
+      <x:c r="B1"/>
+      <x:c r="C1"/>
+      <x:c r="D1"/>
+      <x:c r="E1"/>
+      <x:c r="F1"/>
+      <x:c r="G1"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
+    </x:row>
     <x:row r="3">
+      <x:c r="A3"/>
       <x:c r="B3" s="289" t="str">
         <x:v>Company WorkHub
 企業従業員・タスク管理システム</x:v>
@@ -1397,8 +1700,13 @@
       <x:c r="F3" s="289"/>
       <x:c r="G3" s="289"/>
       <x:c r="H3" s="289"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
+      <x:c r="A4"/>
       <x:c r="B4" s="289"/>
       <x:c r="C4" s="289"/>
       <x:c r="D4" s="289"/>
@@ -1406,8 +1714,13 @@
       <x:c r="F4" s="289"/>
       <x:c r="G4" s="289"/>
       <x:c r="H4" s="289"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5"/>
       <x:c r="B5" s="289"/>
       <x:c r="C5" s="289"/>
       <x:c r="D5" s="289"/>
@@ -1415,8 +1728,13 @@
       <x:c r="F5" s="289"/>
       <x:c r="G5" s="289"/>
       <x:c r="H5" s="289"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
+      <x:c r="A6"/>
       <x:c r="B6"/>
       <x:c r="C6"/>
       <x:c r="D6"/>
@@ -1424,8 +1742,27 @@
       <x:c r="F6"/>
       <x:c r="G6"/>
       <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8">
+      <x:c r="A8"/>
       <x:c r="B8" s="295" t="str">
         <x:v>画面共通設計書</x:v>
       </x:c>
@@ -1435,8 +1772,13 @@
       <x:c r="F8" s="295"/>
       <x:c r="G8" s="295"/>
       <x:c r="H8" s="295"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9">
+      <x:c r="A9"/>
       <x:c r="B9" s="295"/>
       <x:c r="C9" s="295"/>
       <x:c r="D9" s="295"/>
@@ -1444,8 +1786,13 @@
       <x:c r="F9" s="295"/>
       <x:c r="G9" s="295"/>
       <x:c r="H9" s="295"/>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10">
+      <x:c r="A10"/>
       <x:c r="B10" s="295"/>
       <x:c r="C10" s="295"/>
       <x:c r="D10" s="295"/>
@@ -1453,49 +1800,84 @@
       <x:c r="F10" s="295"/>
       <x:c r="G10" s="295"/>
       <x:c r="H10" s="295"/>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11">
+      <x:c r="A11"/>
       <x:c r="B11"/>
-      <x:c r="C11" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="C11" s="339" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
       <x:c r="F11"/>
       <x:c r="G11"/>
       <x:c r="H11"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12">
-      <x:c r="C12" s="297" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="A12"/>
+      <x:c r="B12"/>
+      <x:c r="C12" s="346" t="str">
+        <x:v>Document ID</x:v>
       </x:c>
       <x:c r="D12" s="259" t="str">
         <x:v>CW-BD-SCR-CMN</x:v>
       </x:c>
       <x:c r="E12" s="259"/>
       <x:c r="F12" s="259"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13">
+      <x:c r="A13"/>
+      <x:c r="B13"/>
       <x:c r="C13" s="297" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="D13" s="259" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="D13" s="347" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="E13" s="259"/>
       <x:c r="F13" s="259"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
       <x:c r="C14" s="297" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="D14" s="259" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="D14" s="347" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="E14" s="259"/>
       <x:c r="F14" s="259"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
       <x:c r="C15" s="297" t="str">
         <x:v>作成者</x:v>
       </x:c>
@@ -1504,6 +1886,12 @@
       </x:c>
       <x:c r="E15" s="259"/>
       <x:c r="F15" s="259"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16"/>
@@ -1511,24 +1899,35 @@
       <x:c r="C16" s="297" t="str">
         <x:v>状態</x:v>
       </x:c>
-      <x:c r="D16" s="259" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="D16" s="347" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="E16" s="259"/>
       <x:c r="F16" s="259"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17"/>
-      <x:c r="C17"/>
-      <x:c r="D17"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
+    </x:row>
+    <x:row r="17" ht="26" customHeight="1">
+      <x:c r="A17" s="349"/>
+      <x:c r="B17" s="349"/>
+      <x:c r="C17" s="349"/>
+      <x:c r="D17" s="349"/>
       <x:c r="E17"/>
       <x:c r="F17"/>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="B18"/>
-      <x:c r="C18"/>
-      <x:c r="D18"/>
+    <x:row r="18" ht="26" customHeight="1">
+      <x:c r="A18" s="349"/>
+      <x:c r="B18" s="349"/>
+      <x:c r="C18" s="349" t="str">
+        <x:v>Baseline ID</x:v>
+      </x:c>
+      <x:c r="D18" s="349" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
       <x:c r="E18"/>
       <x:c r="F18"/>
     </x:row>
@@ -1595,6 +1994,387 @@
     <x:mergeCell ref="D15:F15"/>
     <x:mergeCell ref="D16:F16"/>
     <x:mergeCell ref="B19:H21"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="92" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="354" t="str">
+        <x:v>21_ValidationLifecycle</x:v>
+      </x:c>
+      <x:c r="B1" s="353"/>
+      <x:c r="C1" s="353"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="353"/>
+      <x:c r="B2" s="353"/>
+      <x:c r="C2" s="353"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="353" t="str">
+        <x:v>Company WorkHub</x:v>
+      </x:c>
+      <x:c r="B3" s="353"/>
+      <x:c r="C3" s="353"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="353"/>
+      <x:c r="B4" s="353"/>
+      <x:c r="C4" s="353"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="353" t="str">
+        <x:v>BL-2026-09-24 / Review中</x:v>
+      </x:c>
+      <x:c r="B5" s="353"/>
+      <x:c r="C5" s="353"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="353"/>
+      <x:c r="B6" s="353"/>
+      <x:c r="C6" s="353"/>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
+      <x:c r="A7" s="356" t="str">
+        <x:v>Rule ID</x:v>
+      </x:c>
+      <x:c r="B7" s="356" t="str">
+        <x:v>契機</x:v>
+      </x:c>
+      <x:c r="C7" s="356" t="str">
+        <x:v>共通動作</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="57" customHeight="1">
+      <x:c r="A8" s="358" t="str">
+        <x:v>VC-001</x:v>
+      </x:c>
+      <x:c r="B8" s="358" t="str">
+        <x:v>文字数</x:v>
+      </x:c>
+      <x:c r="C8" s="358" t="str">
+        <x:v>Unicode Code Point単位。合成文字列を正規化・切捨てしない。JavaScriptではArray.from(value).lengthに相当。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="57" customHeight="1">
+      <x:c r="A9" s="357" t="str">
+        <x:v>VC-002</x:v>
+      </x:c>
+      <x:c r="B9" s="357" t="str">
+        <x:v>最大桁</x:v>
+      </x:c>
+      <x:c r="C9" s="357" t="str">
+        <x:v>HTML maxLengthによる切捨ては原則使用しない。超過入力を許しVAL-002でError。例外は画面固有項目に明記。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="57" customHeight="1">
+      <x:c r="A10" s="358" t="str">
+        <x:v>VC-003</x:v>
+      </x:c>
+      <x:c r="B10" s="358" t="str">
+        <x:v>Submit</x:v>
+      </x:c>
+      <x:c r="C10" s="358" t="str">
+        <x:v>表示・活性の入力対象を全件検証。非表示・非活性でも送信する業務必須値は送信契約に従い検証。不正ならAPIを呼ばない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="357" t="str">
+        <x:v>VC-004</x:v>
+      </x:c>
+      <x:c r="B11" s="357" t="str">
+        <x:v>Blur</x:v>
+      </x:c>
+      <x:c r="C11" s="357" t="str">
+        <x:v>当該ITEMのみ再検証。未入力必須も判定する。関連項目比較は当該ITEMに定義された比較を実施。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="57" customHeight="1">
+      <x:c r="A12" s="358" t="str">
+        <x:v>VC-005</x:v>
+      </x:c>
+      <x:c r="B12" s="358" t="str">
+        <x:v>Change</x:v>
+      </x:c>
+      <x:c r="C12" s="358" t="str">
+        <x:v>既存Errorを即時Clearしない。次回Blur/Submitで再検証し、正常になった項目のMessageをClearする。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="57" customHeight="1">
+      <x:c r="A13" s="357" t="str">
+        <x:v>VC-006</x:v>
+      </x:c>
+      <x:c r="B13" s="357" t="str">
+        <x:v>複数Error</x:v>
+      </x:c>
+      <x:c r="C13" s="357" t="str">
+        <x:v>Submit時、画面表示順で最初の表示・活性Error項目へFocus。非活性項目へFocusしない。BlurではFocusを強制移動しない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="72" customHeight="1">
+      <x:c r="A14" s="358" t="str">
+        <x:v>VC-007</x:v>
+      </x:c>
+      <x:c r="B14" s="358" t="str">
+        <x:v>Message</x:v>
+      </x:c>
+      <x:c r="C14" s="358" t="str">
+        <x:v>16_入力チェックのVAL ID→Message ID/Parameterを使用。最終文言は18_メッセージと例外のみ管理。複数違反は必須→最大桁→形式→項目間業務Check順の先頭を項目下表示。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="57" customHeight="1">
+      <x:c r="A15" s="357" t="str">
+        <x:v>VC-008</x:v>
+      </x:c>
+      <x:c r="B15" s="357" t="str">
+        <x:v>Schema異常</x:v>
+      </x:c>
+      <x:c r="C15" s="357" t="str">
+        <x:v>10／19_API共通I-Oの共通Client処理で拒否されたResponseを画面へ正常結果として渡さない。部分的State更新を禁止。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="57" customHeight="1">
+      <x:c r="A16" s="358" t="str">
+        <x:v>VC-009</x:v>
+      </x:c>
+      <x:c r="B16" s="358" t="str">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="C16" s="358" t="str">
+        <x:v>Retry-Afterは10／19_API共通I-O参照。待機中は入力/送信を非活性、Focus変更なし。残秒0で再活性後PasswordへFocus（SCR-001）。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:C1"/>
+    <x:mergeCell ref="A3:C3"/>
+    <x:mergeCell ref="A5:C5"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="354" t="str">
+        <x:v>22_共通例外遷移</x:v>
+      </x:c>
+      <x:c r="B1" s="353"/>
+      <x:c r="C1" s="353"/>
+      <x:c r="D1" s="353"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="353"/>
+      <x:c r="B2" s="353"/>
+      <x:c r="C2" s="353"/>
+      <x:c r="D2" s="353"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="353" t="str">
+        <x:v>Company WorkHub</x:v>
+      </x:c>
+      <x:c r="B3" s="353"/>
+      <x:c r="C3" s="353"/>
+      <x:c r="D3" s="353"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="353"/>
+      <x:c r="B4" s="353"/>
+      <x:c r="C4" s="353"/>
+      <x:c r="D4" s="353"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="353" t="str">
+        <x:v>BL-2026-09-24 / Review中</x:v>
+      </x:c>
+      <x:c r="B5" s="353"/>
+      <x:c r="C5" s="353"/>
+      <x:c r="D5" s="353"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="353"/>
+      <x:c r="B6" s="353"/>
+      <x:c r="C6" s="353"/>
+      <x:c r="D6" s="353"/>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
+      <x:c r="A7" s="356" t="str">
+        <x:v>対象</x:v>
+      </x:c>
+      <x:c r="B7" s="356" t="str">
+        <x:v>条件</x:v>
+      </x:c>
+      <x:c r="C7" s="356" t="str">
+        <x:v>Message参照</x:v>
+      </x:c>
+      <x:c r="D7" s="356" t="str">
+        <x:v>遷移・状態</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="358" t="str">
+        <x:v>従業員</x:v>
+      </x:c>
+      <x:c r="B8" s="358" t="str">
+        <x:v>COMMON-4040／employeeId不正</x:v>
+      </x:c>
+      <x:c r="C8" s="358" t="str">
+        <x:v>MSG-E-002</x:v>
+      </x:c>
+      <x:c r="D8" s="358" t="str">
+        <x:v>SCR-003へ戻り再検索。検索条件保持。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="357" t="str">
+        <x:v>部門</x:v>
+      </x:c>
+      <x:c r="B9" s="357" t="str">
+        <x:v>COMMON-4040／departmentId不正</x:v>
+      </x:c>
+      <x:c r="C9" s="357" t="str">
+        <x:v>MSG-E-002</x:v>
+      </x:c>
+      <x:c r="D9" s="357" t="str">
+        <x:v>SCR-007の選択解除、Tree再取得。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="358" t="str">
+        <x:v>Project/Member</x:v>
+      </x:c>
+      <x:c r="B10" s="358" t="str">
+        <x:v>COMMON-4040／projectId不正</x:v>
+      </x:c>
+      <x:c r="C10" s="358" t="str">
+        <x:v>MSG-E-002</x:v>
+      </x:c>
+      <x:c r="D10" s="358" t="str">
+        <x:v>SCR-008へ戻り再検索。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="57" customHeight="1">
+      <x:c r="A11" s="357" t="str">
+        <x:v>Task/添付</x:v>
+      </x:c>
+      <x:c r="B11" s="357" t="str">
+        <x:v>COMMON-4040／taskId・attachmentId不正</x:v>
+      </x:c>
+      <x:c r="C11" s="357" t="str">
+        <x:v>MSG-E-002</x:v>
+      </x:c>
+      <x:c r="D11" s="357" t="str">
+        <x:v>ADMIN/PMはSCR-013、EMPはSCR-014へ戻り再検索（02 Menu権限）。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="57" customHeight="1">
+      <x:c r="A12" s="358" t="str">
+        <x:v>日報</x:v>
+      </x:c>
+      <x:c r="B12" s="358" t="str">
+        <x:v>COMMON-4040／reportId不正</x:v>
+      </x:c>
+      <x:c r="C12" s="358" t="str">
+        <x:v>MSG-E-002</x:v>
+      </x:c>
+      <x:c r="D12" s="358" t="str">
+        <x:v>SCR-021からの遷移ならSCR-021、それ以外SCR-019へ戻り再検索。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="36" customHeight="1">
+      <x:c r="A13" s="357" t="str">
+        <x:v>通知</x:v>
+      </x:c>
+      <x:c r="B13" s="357" t="str">
+        <x:v>COMMON-4040</x:v>
+      </x:c>
+      <x:c r="C13" s="357" t="str">
+        <x:v>MSG-E-002</x:v>
+      </x:c>
+      <x:c r="D13" s="357" t="str">
+        <x:v>SCR-022再取得。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="57" customHeight="1">
+      <x:c r="A14" s="358" t="str">
+        <x:v>User/Role/Log</x:v>
+      </x:c>
+      <x:c r="B14" s="358" t="str">
+        <x:v>COMMON-4040</x:v>
+      </x:c>
+      <x:c r="C14" s="358" t="str">
+        <x:v>MSG-E-002</x:v>
+      </x:c>
+      <x:c r="D14" s="358" t="str">
+        <x:v>それぞれSCR-023/SCR-024/SCR-025へ。選択解除、一覧再取得。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="87" customHeight="1">
+      <x:c r="A15" s="357" t="str">
+        <x:v>未登録Route</x:v>
+      </x:c>
+      <x:c r="B15" s="357" t="str">
+        <x:v>Route不一致</x:v>
+      </x:c>
+      <x:c r="C15" s="357" t="str">
+        <x:v>MSG-E-002</x:v>
+      </x:c>
+      <x:c r="D15" s="357" t="str">
+        <x:v>認証済はSCR-002、未認証はSCR-001。強制変更中はSCR-026優先。専用不存在時の共通遷移（03／22_共通例外遷移）なし。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="87" customHeight="1">
+      <x:c r="A16" s="358" t="str">
+        <x:v>権限不足</x:v>
+      </x:c>
+      <x:c r="B16" s="358" t="str">
+        <x:v>AUTH-4006</x:v>
+      </x:c>
+      <x:c r="C16" s="358" t="str">
+        <x:v>MSG-E-003</x:v>
+      </x:c>
+      <x:c r="D16" s="358" t="str">
+        <x:v>従業員の対象範囲外は検索条件保持でSCR-003へ。それ以外は対象を表示せずSCR-002へ。強制変更中はSCR-026優先。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="132" customHeight="1">
+      <x:c r="A17" s="357" t="str">
+        <x:v>System/Schema異常</x:v>
+      </x:c>
+      <x:c r="B17" s="357" t="str">
+        <x:v>COMMON-5000相当</x:v>
+      </x:c>
+      <x:c r="C17" s="357" t="str">
+        <x:v>MSG-E-001</x:v>
+      </x:c>
+      <x:c r="D17" s="357" t="str">
+        <x:v>現在画面の共通Error AreaへtraceIdと表示。失敗操作の状態は更新せず入力保持。認証済はホームへ戻る操作を提供（強制変更中はSCR-026）、未認証はSCR-001。専用500画面なし。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="A3:D3"/>
+    <x:mergeCell ref="A5:D5"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1625,6 +2405,10 @@
       <x:c r="F1" s="240"/>
       <x:c r="G1" s="240"/>
       <x:c r="H1" s="240"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="240"/>
@@ -1635,42 +2419,42 @@
       <x:c r="F2" s="240"/>
       <x:c r="G2" s="240"/>
       <x:c r="H2" s="240"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="242" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="202" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C3" s="202"/>
-      <x:c r="D3" s="242" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="E3" s="202" t="str">
-        <x:v>DOCUMENT-REVISION</x:v>
-      </x:c>
-      <x:c r="F3" s="202"/>
-      <x:c r="G3" s="202"/>
-      <x:c r="H3" s="202"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="242" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="202" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="202"/>
-      <x:c r="D4" s="242" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="E4" s="202" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="F4" s="202"/>
-      <x:c r="G4" s="202"/>
-      <x:c r="H4" s="202"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="350" t="str">
+        <x:v>システム名：Company WorkHub</x:v>
+      </x:c>
+      <x:c r="B3" s="151"/>
+      <x:c r="C3" s="151"/>
+      <x:c r="D3" s="350"/>
+      <x:c r="E3" s="151"/>
+      <x:c r="F3" s="151"/>
+      <x:c r="G3" s="151"/>
+      <x:c r="H3" s="151"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="350" t="str">
+        <x:v>版数：Ver.2.5    改訂日：2026-09-24    Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="B4" s="151"/>
+      <x:c r="C4" s="151"/>
+      <x:c r="D4" s="350"/>
+      <x:c r="E4" s="151"/>
+      <x:c r="F4" s="151"/>
+      <x:c r="G4" s="151"/>
+      <x:c r="H4" s="151"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5"/>
@@ -1681,6 +2465,10 @@
       <x:c r="F5"/>
       <x:c r="G5"/>
       <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="243" t="str">
@@ -1693,6 +2481,10 @@
       <x:c r="F6" s="243"/>
       <x:c r="G6" s="243"/>
       <x:c r="H6" s="243"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="249" t="str">
@@ -1702,7 +2494,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="C7" s="249" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>改訂内容</x:v>
       </x:c>
       <x:c r="D7" s="249" t="str">
         <x:v>作成者</x:v>
@@ -1719,6 +2511,10 @@
       <x:c r="H7" s="249" t="str">
         <x:v>備考</x:v>
       </x:c>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="155" t="str">
@@ -1740,11 +2536,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G8" s="155" t="str">
-        <x:v>作成済</x:v>
+        <x:v>作成中</x:v>
       </x:c>
       <x:c r="H8" s="155" t="str">
         <x:v>基本設計初版</x:v>
       </x:c>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="155" t="str">
@@ -1766,11 +2566,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G9" s="155" t="str">
-        <x:v>作成済</x:v>
+        <x:v>作成中</x:v>
       </x:c>
       <x:c r="H9" s="155" t="str">
         <x:v>WF_SCR追加</x:v>
       </x:c>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
       <x:c r="A10" s="155" t="str">
@@ -1792,11 +2596,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G10" s="155" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H10" s="155" t="str">
         <x:v>Leader Review後Baseline化</x:v>
       </x:c>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="155" t="str">
@@ -1818,11 +2626,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G11" s="155" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H11" s="155" t="str">
         <x:v>Review指摘対応</x:v>
       </x:c>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="155" t="str">
@@ -1844,11 +2656,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G12" s="155" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H12" s="155" t="str">
         <x:v>再監査指摘対応</x:v>
       </x:c>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="155" t="str">
@@ -1870,11 +2686,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G13" s="155" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H13" s="155" t="str">
         <x:v>再監査第2回指摘対応</x:v>
       </x:c>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
@@ -1895,12 +2715,16 @@
       <x:c r="F14" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G14" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G14" s="339" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H14" t="str">
         <x:v>再監査残項対応</x:v>
       </x:c>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
@@ -1921,12 +2745,16 @@
       <x:c r="F15" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G15" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G15" s="339" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H15" t="str">
         <x:v>再Review指摘対応</x:v>
       </x:c>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
@@ -1947,25 +2775,209 @@
       <x:c r="F16" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G16" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G16" s="339" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H16" t="str">
         <x:v>最大10回の反復監査対応</x:v>
+      </x:c>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>redirect復帰、共通Header通知遷移・未読取得責務を明確化</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G17" s="339" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>04再Review指摘対応</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="338" t="str">
+        <x:v>Ver.1.9</x:v>
+      </x:c>
+      <x:c r="B18" s="338" t="str">
+        <x:v>2026-08-20</x:v>
+      </x:c>
+      <x:c r="C18" s="338" t="str">
+        <x:v>改訂</x:v>
+      </x:c>
+      <x:c r="D18" s="338" t="str">
+        <x:v>React実装用の画面Route Path、Path Parameter、直接URL規則を追加</x:v>
+      </x:c>
+      <x:c r="E18" s="338" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="F18" s="338" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="G18" s="338" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H18" s="338" t="str">
+        <x:v>反映済</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>従業員・部門業務Review：画面遷移、異常時動作、業務Validationを補完</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G19" s="339" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>第1回業務仕様Review指摘対応</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>従業員・部門業務仕様Review：登録後遷移・入社日検証を明確化</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G20" s="339" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
+        <x:v>第2回業務仕様Review指摘対応</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="110" customHeight="1">
+      <x:c r="A21" s="344" t="str">
+        <x:v>Ver.2.3</x:v>
+      </x:c>
+      <x:c r="B21" s="344" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="C21" s="344" t="str">
+        <x:v>内容・関連Reviewの既確定仕様を整合。業務未決事項は承認待ちとして管理。</x:v>
+      </x:c>
+      <x:c r="D21" s="344" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E21" s="344" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F21" s="344" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G21" s="344" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H21" s="344" t="str">
+        <x:v>2026-09-18指摘対応。正式承認を示すものではない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="40" customHeight="1">
+      <x:c r="A22" s="344" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="B22" s="344" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="C22" s="344" t="str">
+        <x:v>待確認12項目の方針選定、業務/API/DB/画面/運用を連動修正。章立て維持。</x:v>
+      </x:c>
+      <x:c r="D22" s="344" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E22" s="344" t="str">
+        <x:v>未実施</x:v>
+      </x:c>
+      <x:c r="F22" s="344" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="G22" s="344" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H22" s="344" t="str">
+        <x:v>一般社内管理Systemの範囲。旧版はBackup保管。</x:v>
+      </x:c>
+      <x:c r="I22" s="344"/>
+      <x:c r="J22" s="344"/>
+      <x:c r="K22" s="344"/>
+      <x:c r="L22" s="344"/>
+    </x:row>
+    <x:row r="23" ht="100" customHeight="1">
+      <x:c r="A23" s="349" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B23" s="349" t="str">
+        <x:v>2026-09-24</x:v>
+      </x:c>
+      <x:c r="C23" s="349" t="str">
+        <x:v>共通規則・正本参照・構成・文書管理を統合修正。Baseline承認前の最終整合修正。</x:v>
+      </x:c>
+      <x:c r="D23" s="349" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E23" s="349" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F23" s="349" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G23" s="349" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H23" s="349" t="str">
+        <x:v>BL-2026-09-24。責任者・Review者・承認者はProject Leaderが記入。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:H3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:H4"/>
     <x:mergeCell ref="A6:H6"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A4:H4"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1996,6 +3008,10 @@
       <x:c r="F1" s="156"/>
       <x:c r="G1" s="156"/>
       <x:c r="H1" s="156"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="156"/>
@@ -2006,42 +3022,46 @@
       <x:c r="F2" s="156"/>
       <x:c r="G2" s="156"/>
       <x:c r="H2" s="156"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="150" t="str">
         <x:v>システム名</x:v>
       </x:c>
-      <x:c r="B3" s="151" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
+      <x:c r="B3" s="151" t="str"/>
       <x:c r="C3" s="151"/>
-      <x:c r="D3" s="150" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
+      <x:c r="D3" s="150" t="str"/>
       <x:c r="E3" s="151" t="str">
         <x:v>CW-BD-040</x:v>
       </x:c>
       <x:c r="F3" s="151"/>
       <x:c r="G3" s="151"/>
       <x:c r="H3" s="151"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="150" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="151" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
+      <x:c r="A4" s="350" t="str">
+        <x:v>版数：Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B4" s="151"/>
       <x:c r="C4" s="151"/>
-      <x:c r="D4" s="150" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
+      <x:c r="D4" s="150" t="str"/>
       <x:c r="E4" s="151" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="F4" s="151"/>
       <x:c r="G4" s="151"/>
       <x:c r="H4" s="151"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="152"/>
@@ -2052,6 +3072,10 @@
       <x:c r="F5" s="152"/>
       <x:c r="G5" s="152"/>
       <x:c r="H5" s="152"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="153" t="str">
@@ -2064,6 +3088,10 @@
       <x:c r="F6" s="153"/>
       <x:c r="G6" s="153"/>
       <x:c r="H6" s="153"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="154" t="str">
@@ -2090,6 +3118,10 @@
       <x:c r="H7" s="154" t="str">
         <x:v>関連API</x:v>
       </x:c>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="155" t="str">
@@ -2116,6 +3148,10 @@
       <x:c r="H8" s="155" t="str">
         <x:v>API-AUTH-001</x:v>
       </x:c>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="155" t="str">
@@ -2134,14 +3170,18 @@
         <x:v>照会</x:v>
       </x:c>
       <x:c r="F9" s="155" t="str">
-        <x:v>期間変更/詳細遷移</x:v>
+        <x:v>期間指定/表示</x:v>
       </x:c>
       <x:c r="G9" s="155" t="str">
         <x:v>M02</x:v>
       </x:c>
       <x:c r="H9" s="155" t="str">
-        <x:v>API-DASH-001,API-NTF-002</x:v>
-      </x:c>
+        <x:v>API-DASH-001</x:v>
+      </x:c>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
       <x:c r="A10" s="155" t="str">
@@ -2160,7 +3200,7 @@
         <x:v>一覧</x:v>
       </x:c>
       <x:c r="F10" s="155" t="str">
-        <x:v>検索/詳細/Import/Export</x:v>
+        <x:v>初期表示/検索/Clear/新規/詳細/編集/Import/Export/Paging</x:v>
       </x:c>
       <x:c r="G10" s="155" t="str">
         <x:v>M03</x:v>
@@ -2168,6 +3208,10 @@
       <x:c r="H10" s="155" t="str">
         <x:v>API-EMP-001, API-EMP-002, API-EMP-006, API-EMP-007</x:v>
       </x:c>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
       <x:c r="A11" s="155" t="str">
@@ -2186,7 +3230,7 @@
         <x:v>入力</x:v>
       </x:c>
       <x:c r="F11" s="155" t="str">
-        <x:v>保存/取消</x:v>
+        <x:v>初期表示/保存/取消/一時Password確認</x:v>
       </x:c>
       <x:c r="G11" s="155" t="str">
         <x:v>M03</x:v>
@@ -2194,6 +3238,10 @@
       <x:c r="H11" s="155" t="str">
         <x:v>API-EMP-003,API-MST-*</x:v>
       </x:c>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="155" t="str">
@@ -2212,7 +3260,7 @@
         <x:v>入力</x:v>
       </x:c>
       <x:c r="F12" s="155" t="str">
-        <x:v>保存/状態変更/取消</x:v>
+        <x:v>初期表示/保存/退職処理/取消</x:v>
       </x:c>
       <x:c r="G12" s="155" t="str">
         <x:v>M03</x:v>
@@ -2220,6 +3268,10 @@
       <x:c r="H12" s="155" t="str">
         <x:v>API-EMP-002, API-EMP-004, API-EMP-005</x:v>
       </x:c>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
       <x:c r="A13" s="155" t="str">
@@ -2238,7 +3290,7 @@
         <x:v>照会</x:v>
       </x:c>
       <x:c r="F13" s="155" t="str">
-        <x:v>表示/編集遷移</x:v>
+        <x:v>表示/編集遷移/戻る</x:v>
       </x:c>
       <x:c r="G13" s="155" t="str">
         <x:v>M03</x:v>
@@ -2246,6 +3298,10 @@
       <x:c r="H13" s="155" t="str">
         <x:v>API-EMP-002</x:v>
       </x:c>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
       <x:c r="A14" s="155" t="str">
@@ -2264,7 +3320,7 @@
         <x:v>Tree/入力</x:v>
       </x:c>
       <x:c r="F14" s="155" t="str">
-        <x:v>検索/登録/更新/削除</x:v>
+        <x:v>Tree表示/選択/Root新規/子部門追加/登録/更新/停止/削除/取消</x:v>
       </x:c>
       <x:c r="G14" s="155" t="str">
         <x:v>M04</x:v>
@@ -2272,6 +3328,10 @@
       <x:c r="H14" s="155" t="str">
         <x:v>API-DEPT-001～005</x:v>
       </x:c>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
       <x:c r="A15" s="155" t="str">
@@ -2298,6 +3358,10 @@
       <x:c r="H15" s="155" t="str">
         <x:v>API-PRJ-001, API-PRJ-002</x:v>
       </x:c>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
       <x:c r="A16" s="155" t="str">
@@ -2324,6 +3388,10 @@
       <x:c r="H16" s="155" t="str">
         <x:v>API-PRJ-003</x:v>
       </x:c>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
       <x:c r="A17" s="155" t="str">
@@ -2414,7 +3482,7 @@
         <x:v>Task管理</x:v>
       </x:c>
       <x:c r="D20" s="155" t="str">
-        <x:v>全員</x:v>
+        <x:v>管理者/PM</x:v>
       </x:c>
       <x:c r="E20" s="155" t="str">
         <x:v>一覧</x:v>
@@ -2788,717 +3856,1169 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="26" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="222" t="str">
-        <x:v>画面遷移</x:v>
-      </x:c>
-      <x:c r="B1" s="222"/>
-      <x:c r="C1" s="222"/>
-      <x:c r="D1" s="222"/>
-      <x:c r="E1" s="222"/>
-      <x:c r="F1" s="222"/>
-      <x:c r="G1" s="222"/>
-      <x:c r="H1" s="222"/>
+      <x:c r="A1" s="354" t="str">
+        <x:v>13_画面遷移</x:v>
+      </x:c>
+      <x:c r="B1" s="353"/>
+      <x:c r="C1" s="353"/>
+      <x:c r="D1" s="353"/>
+      <x:c r="E1" s="353"/>
+      <x:c r="F1" s="353"/>
+      <x:c r="G1" s="353"/>
+      <x:c r="H1" s="353"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="222"/>
-      <x:c r="B2" s="222"/>
-      <x:c r="C2" s="222"/>
-      <x:c r="D2" s="222"/>
-      <x:c r="E2" s="222"/>
-      <x:c r="F2" s="222"/>
-      <x:c r="G2" s="222"/>
-      <x:c r="H2" s="222"/>
+      <x:c r="A2" s="353"/>
+      <x:c r="B2" s="353"/>
+      <x:c r="C2" s="353"/>
+      <x:c r="D2" s="353"/>
+      <x:c r="E2" s="353"/>
+      <x:c r="F2" s="353"/>
+      <x:c r="G2" s="353"/>
+      <x:c r="H2" s="353"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="224" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="202" t="str">
+      <x:c r="A3" s="353" t="str">
         <x:v>Company WorkHub</x:v>
       </x:c>
-      <x:c r="C3" s="202"/>
-      <x:c r="D3" s="224" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="E3" s="202" t="str">
-        <x:v>CW-BD-041</x:v>
-      </x:c>
-      <x:c r="F3" s="202"/>
-      <x:c r="G3" s="202"/>
-      <x:c r="H3" s="202"/>
+      <x:c r="B3" s="353"/>
+      <x:c r="C3" s="353"/>
+      <x:c r="D3" s="353"/>
+      <x:c r="E3" s="353"/>
+      <x:c r="F3" s="353"/>
+      <x:c r="G3" s="353"/>
+      <x:c r="H3" s="353"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="224" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="202" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="202"/>
-      <x:c r="D4" s="224" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="E4" s="202" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="F4" s="202"/>
-      <x:c r="G4" s="202"/>
-      <x:c r="H4" s="202"/>
+      <x:c r="A4" s="353"/>
+      <x:c r="B4" s="353"/>
+      <x:c r="C4" s="353"/>
+      <x:c r="D4" s="353"/>
+      <x:c r="E4" s="353"/>
+      <x:c r="F4" s="353"/>
+      <x:c r="G4" s="353"/>
+      <x:c r="H4" s="353"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="353" t="str">
+        <x:v>BL-2026-09-24 / Review中</x:v>
+      </x:c>
+      <x:c r="B5" s="353"/>
+      <x:c r="C5" s="353"/>
+      <x:c r="D5" s="353"/>
+      <x:c r="E5" s="353"/>
+      <x:c r="F5" s="353"/>
+      <x:c r="G5" s="353"/>
+      <x:c r="H5" s="353"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="225" t="str">
-        <x:v>1. 主要画面遷移</x:v>
-      </x:c>
-      <x:c r="B6" s="225"/>
-      <x:c r="C6" s="225"/>
-      <x:c r="D6" s="225"/>
-      <x:c r="E6" s="225"/>
-      <x:c r="F6" s="225"/>
-      <x:c r="G6" s="225"/>
-      <x:c r="H6" s="225"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="231" t="str">
+      <x:c r="A6" s="353"/>
+      <x:c r="B6" s="353"/>
+      <x:c r="C6" s="353"/>
+      <x:c r="D6" s="353"/>
+      <x:c r="E6" s="353"/>
+      <x:c r="F6" s="353"/>
+      <x:c r="G6" s="353"/>
+      <x:c r="H6" s="353"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
+      <x:c r="A7" s="356" t="str">
         <x:v>No.</x:v>
       </x:c>
-      <x:c r="B7" s="231" t="str">
+      <x:c r="B7" s="356" t="str">
         <x:v>遷移元</x:v>
       </x:c>
-      <x:c r="C7" s="231" t="str">
+      <x:c r="C7" s="356" t="str">
         <x:v>イベント</x:v>
       </x:c>
-      <x:c r="D7" s="231" t="str">
+      <x:c r="D7" s="356" t="str">
         <x:v>遷移先</x:v>
       </x:c>
-      <x:c r="E7" s="231" t="str">
+      <x:c r="E7" s="356" t="str">
         <x:v>引継情報</x:v>
       </x:c>
-      <x:c r="F7" s="231" t="str">
-        <x:v>権限・条件</x:v>
-      </x:c>
-      <x:c r="G7" s="231" t="str">
+      <x:c r="F7" s="356" t="str">
+        <x:v>権限参照</x:v>
+      </x:c>
+      <x:c r="G7" s="356" t="str">
         <x:v>戻る動作</x:v>
       </x:c>
-      <x:c r="H7" s="231" t="str">
+      <x:c r="H7" s="356" t="str">
         <x:v>備考</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="155" t="n">
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="358" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B8" s="155" t="str">
+      <x:c r="B8" s="358" t="str">
         <x:v>未認証</x:v>
       </x:c>
-      <x:c r="C8" s="155" t="str">
+      <x:c r="C8" s="358" t="str">
         <x:v>URLアクセス</x:v>
       </x:c>
-      <x:c r="D8" s="155" t="str">
+      <x:c r="D8" s="358" t="str">
         <x:v>SCR-001</x:v>
       </x:c>
-      <x:c r="E8" s="155" t="str">
+      <x:c r="E8" s="358" t="str">
         <x:v>redirect URL</x:v>
       </x:c>
-      <x:c r="F8" s="155" t="str">
-        <x:v>Tokenなし/無効</x:v>
-      </x:c>
-      <x:c r="G8" s="155" t="str">
+      <x:c r="F8" s="358" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G8" s="358" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="H8" s="155"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="155" t="n">
+      <x:c r="H8" s="358" t="str"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
+    </x:row>
+    <x:row r="9" ht="57" customHeight="1">
+      <x:c r="A9" s="357" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B9" s="155" t="str">
+      <x:c r="B9" s="357" t="str">
         <x:v>SCR-001</x:v>
       </x:c>
-      <x:c r="C9" s="155" t="str">
+      <x:c r="C9" s="357" t="str">
         <x:v>ログイン成功</x:v>
       </x:c>
-      <x:c r="D9" s="155" t="str">
+      <x:c r="D9" s="357" t="str">
+        <x:v>SCR-026（変更必須）／許可redirect先（設定あり）／SCR-002（他）</x:v>
+      </x:c>
+      <x:c r="E9" s="357" t="str">
+        <x:v>redirect URL,ユーザー/権限/Menu</x:v>
+      </x:c>
+      <x:c r="F9" s="357" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G9" s="357" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H9" s="357" t="str">
+        <x:v>03／20_画面Route定義の優先順位で一意に判定。</x:v>
+      </x:c>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="358" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B10" s="358" t="str">
+        <x:v>共通Header</x:v>
+      </x:c>
+      <x:c r="C10" s="358" t="str">
+        <x:v>ログアウト</x:v>
+      </x:c>
+      <x:c r="D10" s="358" t="str">
+        <x:v>SCR-001</x:v>
+      </x:c>
+      <x:c r="E10" s="358" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="F10" s="358" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G10" s="358" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H10" s="358" t="str">
+        <x:v>MSG-C-003確認あり</x:v>
+      </x:c>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="357" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B11" s="357" t="str">
+        <x:v>SCR-008</x:v>
+      </x:c>
+      <x:c r="C11" s="357" t="str">
+        <x:v>新規</x:v>
+      </x:c>
+      <x:c r="D11" s="357" t="str">
+        <x:v>SCR-009</x:v>
+      </x:c>
+      <x:c r="E11" s="357" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="F11" s="357" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G11" s="357" t="str">
+        <x:v>一覧へ</x:v>
+      </x:c>
+      <x:c r="H11" s="357" t="str"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="358" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B12" s="358" t="str">
+        <x:v>SCR-008</x:v>
+      </x:c>
+      <x:c r="C12" s="358" t="str">
+        <x:v>詳細/編集</x:v>
+      </x:c>
+      <x:c r="D12" s="358" t="str">
+        <x:v>SCR-011 / SCR-010</x:v>
+      </x:c>
+      <x:c r="E12" s="358" t="str">
+        <x:v>projectId</x:v>
+      </x:c>
+      <x:c r="F12" s="358" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G12" s="358" t="str">
+        <x:v>検索条件保持</x:v>
+      </x:c>
+      <x:c r="H12" s="358" t="str"/>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="357" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B13" s="357" t="str">
+        <x:v>SCR-011</x:v>
+      </x:c>
+      <x:c r="C13" s="357" t="str">
+        <x:v>メンバー管理</x:v>
+      </x:c>
+      <x:c r="D13" s="357" t="str">
+        <x:v>SCR-012</x:v>
+      </x:c>
+      <x:c r="E13" s="357" t="str">
+        <x:v>projectId</x:v>
+      </x:c>
+      <x:c r="F13" s="357" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G13" s="357" t="str">
+        <x:v>詳細へ</x:v>
+      </x:c>
+      <x:c r="H13" s="357" t="str"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
+    </x:row>
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="358" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B14" s="358" t="str">
+        <x:v>SCR-013 / SCR-014</x:v>
+      </x:c>
+      <x:c r="C14" s="358" t="str">
+        <x:v>新規</x:v>
+      </x:c>
+      <x:c r="D14" s="358" t="str">
+        <x:v>SCR-015</x:v>
+      </x:c>
+      <x:c r="E14" s="358" t="str">
+        <x:v>projectId</x:v>
+      </x:c>
+      <x:c r="F14" s="358" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G14" s="358" t="str">
+        <x:v>一覧へ</x:v>
+      </x:c>
+      <x:c r="H14" s="358" t="str"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
+    </x:row>
+    <x:row r="15" ht="42" customHeight="1">
+      <x:c r="A15" s="357" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B15" s="357" t="str">
+        <x:v>SCR-013 / SCR-014</x:v>
+      </x:c>
+      <x:c r="C15" s="357" t="str">
+        <x:v>詳細</x:v>
+      </x:c>
+      <x:c r="D15" s="357" t="str">
+        <x:v>SCR-017</x:v>
+      </x:c>
+      <x:c r="E15" s="357" t="str">
+        <x:v>taskId</x:v>
+      </x:c>
+      <x:c r="F15" s="357" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G15" s="357" t="str">
+        <x:v>検索条件保持</x:v>
+      </x:c>
+      <x:c r="H15" s="357" t="str"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
+    </x:row>
+    <x:row r="16" ht="42" customHeight="1">
+      <x:c r="A16" s="358" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B16" s="358" t="str">
+        <x:v>SCR-017</x:v>
+      </x:c>
+      <x:c r="C16" s="358" t="str">
+        <x:v>編集</x:v>
+      </x:c>
+      <x:c r="D16" s="358" t="str">
+        <x:v>SCR-016</x:v>
+      </x:c>
+      <x:c r="E16" s="358" t="str">
+        <x:v>taskId/version</x:v>
+      </x:c>
+      <x:c r="F16" s="358" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G16" s="358" t="str">
+        <x:v>詳細へ</x:v>
+      </x:c>
+      <x:c r="H16" s="358" t="str"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
+    </x:row>
+    <x:row r="17" ht="42" customHeight="1">
+      <x:c r="A17" s="357" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B17" s="357" t="str">
+        <x:v>SCR-018</x:v>
+      </x:c>
+      <x:c r="C17" s="357" t="str">
+        <x:v>カード選択</x:v>
+      </x:c>
+      <x:c r="D17" s="357" t="str">
+        <x:v>SCR-017</x:v>
+      </x:c>
+      <x:c r="E17" s="357" t="str">
+        <x:v>taskId</x:v>
+      </x:c>
+      <x:c r="F17" s="357" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G17" s="357" t="str">
+        <x:v>看板へ</x:v>
+      </x:c>
+      <x:c r="H17" s="357" t="str"/>
+    </x:row>
+    <x:row r="18" ht="42" customHeight="1">
+      <x:c r="A18" s="358" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B18" s="358" t="str">
+        <x:v>SCR-019</x:v>
+      </x:c>
+      <x:c r="C18" s="358" t="str">
+        <x:v>新規/編集</x:v>
+      </x:c>
+      <x:c r="D18" s="358" t="str">
+        <x:v>SCR-020</x:v>
+      </x:c>
+      <x:c r="E18" s="358" t="str">
+        <x:v>reportId/date</x:v>
+      </x:c>
+      <x:c r="F18" s="358" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G18" s="358" t="str">
+        <x:v>一覧へ</x:v>
+      </x:c>
+      <x:c r="H18" s="358" t="str"/>
+    </x:row>
+    <x:row r="19" ht="42" customHeight="1">
+      <x:c r="A19" s="357" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B19" s="357" t="str">
+        <x:v>共通Header</x:v>
+      </x:c>
+      <x:c r="C19" s="357" t="str">
+        <x:v>通知アイコン/未読件数</x:v>
+      </x:c>
+      <x:c r="D19" s="357" t="str">
+        <x:v>SCR-022</x:v>
+      </x:c>
+      <x:c r="E19" s="357" t="str">
+        <x:v>遷移元Route</x:v>
+      </x:c>
+      <x:c r="F19" s="357" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G19" s="357" t="str">
+        <x:v>元画面へ</x:v>
+      </x:c>
+      <x:c r="H19" s="357" t="str">
+        <x:v>共通Header機能</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="42" customHeight="1">
+      <x:c r="A20" s="358" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B20" s="358" t="str">
+        <x:v>共通ユーザーMenu</x:v>
+      </x:c>
+      <x:c r="C20" s="358" t="str">
+        <x:v>Password変更</x:v>
+      </x:c>
+      <x:c r="D20" s="358" t="str">
+        <x:v>SCR-026</x:v>
+      </x:c>
+      <x:c r="E20" s="358" t="str">
+        <x:v>遷移元Route</x:v>
+      </x:c>
+      <x:c r="F20" s="358" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G20" s="358" t="str">
+        <x:v>元画面へ</x:v>
+      </x:c>
+      <x:c r="H20" s="358" t="str">
+        <x:v>取消時に復帰</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="42" customHeight="1">
+      <x:c r="A21" s="357" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B21" s="357" t="str">
+        <x:v>任意画面</x:v>
+      </x:c>
+      <x:c r="C21" s="357" t="str">
+        <x:v>Token期限切れ</x:v>
+      </x:c>
+      <x:c r="D21" s="357" t="str">
+        <x:v>SCR-001</x:v>
+      </x:c>
+      <x:c r="E21" s="357" t="str">
+        <x:v>redirect URL</x:v>
+      </x:c>
+      <x:c r="F21" s="357" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G21" s="357" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H21" s="357" t="str">
+        <x:v>MSG-E-005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="42" customHeight="1">
+      <x:c r="A22" s="358" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B22" s="358" t="str">
+        <x:v>共通Menu</x:v>
+      </x:c>
+      <x:c r="C22" s="358" t="str">
+        <x:v>Task一覧</x:v>
+      </x:c>
+      <x:c r="D22" s="358" t="str">
+        <x:v>SCR-013</x:v>
+      </x:c>
+      <x:c r="E22" s="358" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="F22" s="358" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G22" s="358" t="str">
+        <x:v>元画面へ</x:v>
+      </x:c>
+      <x:c r="H22" s="358" t="str">
+        <x:v>Menu権限</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="42" customHeight="1">
+      <x:c r="A23" s="357" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B23" s="357" t="str">
+        <x:v>共通Menu</x:v>
+      </x:c>
+      <x:c r="C23" s="357" t="str">
+        <x:v>マイTask</x:v>
+      </x:c>
+      <x:c r="D23" s="357" t="str">
+        <x:v>SCR-014</x:v>
+      </x:c>
+      <x:c r="E23" s="357" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="F23" s="357" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G23" s="357" t="str">
+        <x:v>元画面へ</x:v>
+      </x:c>
+      <x:c r="H23" s="357" t="str">
+        <x:v>Menu権限</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="42" customHeight="1">
+      <x:c r="A24" s="358" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B24" s="358" t="str">
+        <x:v>共通Menu</x:v>
+      </x:c>
+      <x:c r="C24" s="358" t="str">
+        <x:v>日報検索</x:v>
+      </x:c>
+      <x:c r="D24" s="358" t="str">
+        <x:v>SCR-021</x:v>
+      </x:c>
+      <x:c r="E24" s="358" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="F24" s="358" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G24" s="358" t="str">
+        <x:v>元画面へ</x:v>
+      </x:c>
+      <x:c r="H24" s="358" t="str">
+        <x:v>Menu権限</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="42" customHeight="1">
+      <x:c r="A25" s="357" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B25" s="357" t="str">
+        <x:v>共通Menu</x:v>
+      </x:c>
+      <x:c r="C25" s="357" t="str">
+        <x:v>User管理</x:v>
+      </x:c>
+      <x:c r="D25" s="357" t="str">
+        <x:v>SCR-023</x:v>
+      </x:c>
+      <x:c r="E25" s="357" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="F25" s="357" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G25" s="357" t="str">
+        <x:v>元画面へ</x:v>
+      </x:c>
+      <x:c r="H25" s="357" t="str">
+        <x:v>Menu権限</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="42" customHeight="1">
+      <x:c r="A26" s="358" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B26" s="358" t="str">
+        <x:v>共通Menu</x:v>
+      </x:c>
+      <x:c r="C26" s="358" t="str">
+        <x:v>Role管理</x:v>
+      </x:c>
+      <x:c r="D26" s="358" t="str">
+        <x:v>SCR-024</x:v>
+      </x:c>
+      <x:c r="E26" s="358" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="F26" s="358" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G26" s="358" t="str">
+        <x:v>元画面へ</x:v>
+      </x:c>
+      <x:c r="H26" s="358" t="str">
+        <x:v>Menu権限</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="42" customHeight="1">
+      <x:c r="A27" s="357" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B27" s="357" t="str">
+        <x:v>共通Menu</x:v>
+      </x:c>
+      <x:c r="C27" s="357" t="str">
+        <x:v>操作Log</x:v>
+      </x:c>
+      <x:c r="D27" s="357" t="str">
+        <x:v>SCR-025</x:v>
+      </x:c>
+      <x:c r="E27" s="357" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="F27" s="357" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G27" s="357" t="str">
+        <x:v>元画面へ</x:v>
+      </x:c>
+      <x:c r="H27" s="357" t="str">
+        <x:v>Menu権限</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="42" customHeight="1">
+      <x:c r="A28" s="358" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B28" s="358" t="str">
+        <x:v>共通Menu</x:v>
+      </x:c>
+      <x:c r="C28" s="358" t="str">
+        <x:v>従業員管理</x:v>
+      </x:c>
+      <x:c r="D28" s="358" t="str">
+        <x:v>SCR-003</x:v>
+      </x:c>
+      <x:c r="E28" s="358" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="F28" s="358" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G28" s="358" t="str">
+        <x:v>元画面へ</x:v>
+      </x:c>
+      <x:c r="H28" s="358" t="str">
+        <x:v>02／14_DataScope定義 DS-EMP-001参照</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="42" customHeight="1">
+      <x:c r="A29" s="357" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B29" s="357" t="str">
+        <x:v>SCR-003</x:v>
+      </x:c>
+      <x:c r="C29" s="357" t="str">
+        <x:v>新規</x:v>
+      </x:c>
+      <x:c r="D29" s="357" t="str">
+        <x:v>SCR-004</x:v>
+      </x:c>
+      <x:c r="E29" s="357" t="str">
+        <x:v>検索条件/Page/Sort</x:v>
+      </x:c>
+      <x:c r="F29" s="357" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G29" s="357" t="str">
+        <x:v>SCR-003へ戻り検索条件復元</x:v>
+      </x:c>
+      <x:c r="H29" s="357" t="str">
+        <x:v>PMは非表示</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="42" customHeight="1">
+      <x:c r="A30" s="358" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B30" s="358" t="str">
+        <x:v>SCR-003</x:v>
+      </x:c>
+      <x:c r="C30" s="358" t="str">
+        <x:v>詳細</x:v>
+      </x:c>
+      <x:c r="D30" s="358" t="str">
+        <x:v>SCR-006</x:v>
+      </x:c>
+      <x:c r="E30" s="358" t="str">
+        <x:v>employeeId,検索条件/Page/Sort</x:v>
+      </x:c>
+      <x:c r="F30" s="358" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G30" s="358" t="str">
+        <x:v>SCR-003へ戻り検索条件復元</x:v>
+      </x:c>
+      <x:c r="H30" s="358" t="str">
+        <x:v>範囲外は権限Error</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="42" customHeight="1">
+      <x:c r="A31" s="357" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B31" s="357" t="str">
+        <x:v>SCR-003</x:v>
+      </x:c>
+      <x:c r="C31" s="357" t="str">
+        <x:v>編集</x:v>
+      </x:c>
+      <x:c r="D31" s="357" t="str">
+        <x:v>SCR-005</x:v>
+      </x:c>
+      <x:c r="E31" s="357" t="str">
+        <x:v>employeeId,検索条件/Page/Sort</x:v>
+      </x:c>
+      <x:c r="F31" s="357" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G31" s="357" t="str">
+        <x:v>SCR-003へ戻り検索条件復元</x:v>
+      </x:c>
+      <x:c r="H31" s="357" t="str">
+        <x:v>PMは非表示</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="57" customHeight="1">
+      <x:c r="A32" s="358" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B32" s="358" t="str">
+        <x:v>SCR-004</x:v>
+      </x:c>
+      <x:c r="C32" s="358" t="str">
+        <x:v>登録成功・一時Password確認完了</x:v>
+      </x:c>
+      <x:c r="D32" s="358" t="str">
+        <x:v>SCR-003</x:v>
+      </x:c>
+      <x:c r="E32" s="358" t="str">
+        <x:v>登録employeeId/employeeCode</x:v>
+      </x:c>
+      <x:c r="F32" s="358" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G32" s="358" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H32" s="358" t="str">
+        <x:v>社員番号=登録社員番号、他条件空欄、page=0で再検索</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="42" customHeight="1">
+      <x:c r="A33" s="357" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B33" s="357" t="str">
+        <x:v>SCR-004</x:v>
+      </x:c>
+      <x:c r="C33" s="357" t="str">
+        <x:v>取消</x:v>
+      </x:c>
+      <x:c r="D33" s="357" t="str">
+        <x:v>SCR-003</x:v>
+      </x:c>
+      <x:c r="E33" s="357" t="str">
+        <x:v>検索条件/Page/Sort</x:v>
+      </x:c>
+      <x:c r="F33" s="357" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G33" s="357" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H33" s="357" t="str">
+        <x:v>入力済みの場合は破棄確認</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="42" customHeight="1">
+      <x:c r="A34" s="358" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B34" s="358" t="str">
+        <x:v>SCR-005</x:v>
+      </x:c>
+      <x:c r="C34" s="358" t="str">
+        <x:v>保存成功</x:v>
+      </x:c>
+      <x:c r="D34" s="358" t="str">
+        <x:v>SCR-006</x:v>
+      </x:c>
+      <x:c r="E34" s="358" t="str">
+        <x:v>employeeId,検索条件/Page/Sort</x:v>
+      </x:c>
+      <x:c r="F34" s="358" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G34" s="358" t="str">
+        <x:v>SCR-003へ戻る</x:v>
+      </x:c>
+      <x:c r="H34" s="358" t="str">
+        <x:v>更新後Dataを再取得</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="42" customHeight="1">
+      <x:c r="A35" s="357" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B35" s="357" t="str">
+        <x:v>SCR-005</x:v>
+      </x:c>
+      <x:c r="C35" s="357" t="str">
+        <x:v>退職成功</x:v>
+      </x:c>
+      <x:c r="D35" s="357" t="str">
+        <x:v>SCR-006</x:v>
+      </x:c>
+      <x:c r="E35" s="357" t="str">
+        <x:v>employeeId,検索条件/Page/Sort</x:v>
+      </x:c>
+      <x:c r="F35" s="357" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G35" s="357" t="str">
+        <x:v>SCR-003へ戻る</x:v>
+      </x:c>
+      <x:c r="H35" s="357" t="str">
+        <x:v>LEFT状態を表示</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="42" customHeight="1">
+      <x:c r="A36" s="358" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B36" s="358" t="str">
+        <x:v>SCR-005</x:v>
+      </x:c>
+      <x:c r="C36" s="358" t="str">
+        <x:v>取消</x:v>
+      </x:c>
+      <x:c r="D36" s="358" t="str">
+        <x:v>SCR-006</x:v>
+      </x:c>
+      <x:c r="E36" s="358" t="str">
+        <x:v>employeeId,検索条件/Page/Sort</x:v>
+      </x:c>
+      <x:c r="F36" s="358" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G36" s="358" t="str">
+        <x:v>SCR-003へ戻る</x:v>
+      </x:c>
+      <x:c r="H36" s="358" t="str">
+        <x:v>変更ありの場合は破棄確認</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="42" customHeight="1">
+      <x:c r="A37" s="357" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B37" s="357" t="str">
+        <x:v>SCR-006</x:v>
+      </x:c>
+      <x:c r="C37" s="357" t="str">
+        <x:v>編集</x:v>
+      </x:c>
+      <x:c r="D37" s="357" t="str">
+        <x:v>SCR-005</x:v>
+      </x:c>
+      <x:c r="E37" s="357" t="str">
+        <x:v>employeeId,検索条件/Page/Sort</x:v>
+      </x:c>
+      <x:c r="F37" s="357" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G37" s="357" t="str">
+        <x:v>SCR-006へ</x:v>
+      </x:c>
+      <x:c r="H37" s="357" t="str">
+        <x:v>PMは非表示</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="42" customHeight="1">
+      <x:c r="A38" s="358" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B38" s="358" t="str">
+        <x:v>SCR-006</x:v>
+      </x:c>
+      <x:c r="C38" s="358" t="str">
+        <x:v>戻る</x:v>
+      </x:c>
+      <x:c r="D38" s="358" t="str">
+        <x:v>SCR-003</x:v>
+      </x:c>
+      <x:c r="E38" s="358" t="str">
+        <x:v>検索条件/Page/Sort</x:v>
+      </x:c>
+      <x:c r="F38" s="358" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G38" s="358" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H38" s="358" t="str">
+        <x:v>検索条件/Pageを復元</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="42" customHeight="1">
+      <x:c r="A39" s="357" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B39" s="357" t="str">
+        <x:v>共通Menu</x:v>
+      </x:c>
+      <x:c r="C39" s="357" t="str">
+        <x:v>部門管理</x:v>
+      </x:c>
+      <x:c r="D39" s="357" t="str">
+        <x:v>SCR-007</x:v>
+      </x:c>
+      <x:c r="E39" s="357" t="str">
+        <x:v>遷移元Route</x:v>
+      </x:c>
+      <x:c r="F39" s="357" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G39" s="357" t="str">
+        <x:v>元画面へ</x:v>
+      </x:c>
+      <x:c r="H39" s="357" t="str">
+        <x:v>Menu権限</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="42" customHeight="1">
+      <x:c r="A40" s="358" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B40" s="358" t="str">
+        <x:v>SCR-007</x:v>
+      </x:c>
+      <x:c r="C40" s="358" t="str">
+        <x:v>戻る</x:v>
+      </x:c>
+      <x:c r="D40" s="358" t="str">
+        <x:v>遷移元画面</x:v>
+      </x:c>
+      <x:c r="E40" s="358" t="str">
+        <x:v>遷移元Route</x:v>
+      </x:c>
+      <x:c r="F40" s="358" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G40" s="358" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H40" s="358" t="str">
+        <x:v>未保存時は破棄確認</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="42" customHeight="1">
+      <x:c r="A41" s="357" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B41" s="357" t="str">
+        <x:v>未認証</x:v>
+      </x:c>
+      <x:c r="C41" s="357" t="str">
+        <x:v>保護URLアクセス</x:v>
+      </x:c>
+      <x:c r="D41" s="357" t="str">
+        <x:v>SCR-001</x:v>
+      </x:c>
+      <x:c r="E41" s="357" t="str">
+        <x:v>redirect URL</x:v>
+      </x:c>
+      <x:c r="F41" s="357" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G41" s="357" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H41" s="357" t="str">
+        <x:v>Route Guardで保持</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="42" customHeight="1">
+      <x:c r="A42" s="358" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B42" s="358" t="str">
+        <x:v>SCR-001</x:v>
+      </x:c>
+      <x:c r="C42" s="358" t="str">
+        <x:v>ログイン成功（redirect有効）</x:v>
+      </x:c>
+      <x:c r="D42" s="358" t="str">
+        <x:v>redirect対象画面</x:v>
+      </x:c>
+      <x:c r="E42" s="358" t="str">
+        <x:v>redirect URL,User/権限/Menu</x:v>
+      </x:c>
+      <x:c r="F42" s="358" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G42" s="358" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H42" s="358" t="str">
+        <x:v>API-AUTH-004後に遷移</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="42" customHeight="1">
+      <x:c r="A43" s="357" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B43" s="357" t="str">
+        <x:v>SCR-001</x:v>
+      </x:c>
+      <x:c r="C43" s="357" t="str">
+        <x:v>ログイン成功（redirectなし/無効）</x:v>
+      </x:c>
+      <x:c r="D43" s="357" t="str">
         <x:v>SCR-002</x:v>
       </x:c>
-      <x:c r="E9" s="155" t="str">
-        <x:v>ユーザー/権限</x:v>
-      </x:c>
-      <x:c r="F9" s="155" t="str">
-        <x:v>有効ユーザー</x:v>
-      </x:c>
-      <x:c r="G9" s="155" t="str">
+      <x:c r="E43" s="357" t="str">
+        <x:v>User/権限/Menu</x:v>
+      </x:c>
+      <x:c r="F43" s="357" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G43" s="357" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="H9" s="155"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="155" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B10" s="155" t="str">
+      <x:c r="H43" s="357" t="str">
+        <x:v>既定遷移</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="42" customHeight="1">
+      <x:c r="A44" s="358" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B44" s="358" t="str">
+        <x:v>SCR-013, SCR-014</x:v>
+      </x:c>
+      <x:c r="C44" s="358" t="str">
+        <x:v>新規</x:v>
+      </x:c>
+      <x:c r="D44" s="358" t="str">
+        <x:v>SCR-015</x:v>
+      </x:c>
+      <x:c r="E44" s="358" t="str">
+        <x:v>projectId</x:v>
+      </x:c>
+      <x:c r="F44" s="358" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G44" s="358" t="str">
+        <x:v>一覧へ</x:v>
+      </x:c>
+      <x:c r="H44" s="358" t="str"/>
+    </x:row>
+    <x:row r="45" ht="42" customHeight="1">
+      <x:c r="A45" s="357" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B45" s="357" t="str">
+        <x:v>SCR-013, SCR-014</x:v>
+      </x:c>
+      <x:c r="C45" s="357" t="str">
+        <x:v>詳細</x:v>
+      </x:c>
+      <x:c r="D45" s="357" t="str">
+        <x:v>SCR-017</x:v>
+      </x:c>
+      <x:c r="E45" s="357" t="str">
+        <x:v>taskId</x:v>
+      </x:c>
+      <x:c r="F45" s="357" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G45" s="357" t="str">
+        <x:v>検索条件保持</x:v>
+      </x:c>
+      <x:c r="H45" s="357" t="str"/>
+    </x:row>
+    <x:row r="46" ht="72" customHeight="1">
+      <x:c r="A46" s="358" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B46" s="358" t="str">
         <x:v>共通Header</x:v>
       </x:c>
-      <x:c r="C10" s="155" t="str">
-        <x:v>ログアウト</x:v>
-      </x:c>
-      <x:c r="D10" s="155" t="str">
-        <x:v>SCR-001</x:v>
-      </x:c>
-      <x:c r="E10" s="155" t="str">
+      <x:c r="C46" s="358" t="str">
+        <x:v>通知Bell／未読件数Click</x:v>
+      </x:c>
+      <x:c r="D46" s="358" t="str">
+        <x:v>SCR-022</x:v>
+      </x:c>
+      <x:c r="E46" s="358" t="str">
         <x:v>なし</x:v>
       </x:c>
-      <x:c r="F10" s="155" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="G10" s="155" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="H10" s="155" t="str">
-        <x:v>確認あり</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="155" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B11" s="155" t="str">
-        <x:v>SCR-003</x:v>
-      </x:c>
-      <x:c r="C11" s="155" t="str">
-        <x:v>新規</x:v>
-      </x:c>
-      <x:c r="D11" s="155" t="str">
-        <x:v>SCR-004</x:v>
-      </x:c>
-      <x:c r="E11" s="155" t="str">
-        <x:v>なし</x:v>
-      </x:c>
-      <x:c r="F11" s="155" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="G11" s="155" t="str">
-        <x:v>一覧へ</x:v>
-      </x:c>
-      <x:c r="H11" s="155"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="155" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B12" s="155" t="str">
-        <x:v>SCR-003</x:v>
-      </x:c>
-      <x:c r="C12" s="155" t="str">
-        <x:v>詳細/編集</x:v>
-      </x:c>
-      <x:c r="D12" s="155" t="str">
-        <x:v>SCR-006 / SCR-005</x:v>
-      </x:c>
-      <x:c r="E12" s="155" t="str">
-        <x:v>employeeId</x:v>
-      </x:c>
-      <x:c r="F12" s="155" t="str">
-        <x:v>参照/更新権限</x:v>
-      </x:c>
-      <x:c r="G12" s="155" t="str">
-        <x:v>検索条件を保持</x:v>
-      </x:c>
-      <x:c r="H12" s="155"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="155" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B13" s="155" t="str">
-        <x:v>SCR-008</x:v>
-      </x:c>
-      <x:c r="C13" s="155" t="str">
-        <x:v>新規</x:v>
-      </x:c>
-      <x:c r="D13" s="155" t="str">
-        <x:v>SCR-009</x:v>
-      </x:c>
-      <x:c r="E13" s="155" t="str">
-        <x:v>なし</x:v>
-      </x:c>
-      <x:c r="F13" s="155" t="str">
-        <x:v>管理者</x:v>
-      </x:c>
-      <x:c r="G13" s="155" t="str">
-        <x:v>一覧へ</x:v>
-      </x:c>
-      <x:c r="H13" s="155"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="155" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B14" s="155" t="str">
-        <x:v>SCR-008</x:v>
-      </x:c>
-      <x:c r="C14" s="155" t="str">
-        <x:v>詳細/編集</x:v>
-      </x:c>
-      <x:c r="D14" s="155" t="str">
-        <x:v>SCR-011 / SCR-010</x:v>
-      </x:c>
-      <x:c r="E14" s="155" t="str">
-        <x:v>projectId</x:v>
-      </x:c>
-      <x:c r="F14" s="155" t="str">
-        <x:v>関係者/担当PM</x:v>
-      </x:c>
-      <x:c r="G14" s="155" t="str">
-        <x:v>検索条件保持</x:v>
-      </x:c>
-      <x:c r="H14" s="155"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="155" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B15" s="155" t="str">
-        <x:v>SCR-011</x:v>
-      </x:c>
-      <x:c r="C15" s="155" t="str">
-        <x:v>メンバー管理</x:v>
-      </x:c>
-      <x:c r="D15" s="155" t="str">
-        <x:v>SCR-012</x:v>
-      </x:c>
-      <x:c r="E15" s="155" t="str">
-        <x:v>projectId</x:v>
-      </x:c>
-      <x:c r="F15" s="155" t="str">
-        <x:v>管理者/担当PM</x:v>
-      </x:c>
-      <x:c r="G15" s="155" t="str">
-        <x:v>詳細へ</x:v>
-      </x:c>
-      <x:c r="H15" s="155"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="155" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B16" s="155" t="str">
-        <x:v>SCR-013 / SCR-014</x:v>
-      </x:c>
-      <x:c r="C16" s="155" t="str">
-        <x:v>新規</x:v>
-      </x:c>
-      <x:c r="D16" s="155" t="str">
-        <x:v>SCR-015</x:v>
-      </x:c>
-      <x:c r="E16" s="155" t="str">
-        <x:v>projectId</x:v>
-      </x:c>
-      <x:c r="F16" s="155" t="str">
-        <x:v>管理者/担当PM</x:v>
-      </x:c>
-      <x:c r="G16" s="155" t="str">
-        <x:v>一覧へ</x:v>
-      </x:c>
-      <x:c r="H16" s="155"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="155" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B17" s="155" t="str">
-        <x:v>SCR-013 / SCR-014</x:v>
-      </x:c>
-      <x:c r="C17" s="155" t="str">
-        <x:v>詳細</x:v>
-      </x:c>
-      <x:c r="D17" s="155" t="str">
-        <x:v>SCR-017</x:v>
-      </x:c>
-      <x:c r="E17" s="155" t="str">
-        <x:v>taskId</x:v>
-      </x:c>
-      <x:c r="F17" s="155" t="str">
-        <x:v>Task関係者</x:v>
-      </x:c>
-      <x:c r="G17" s="155" t="str">
-        <x:v>検索条件保持</x:v>
-      </x:c>
-      <x:c r="H17" s="155"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="155" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B18" s="155" t="str">
-        <x:v>SCR-017</x:v>
-      </x:c>
-      <x:c r="C18" s="155" t="str">
-        <x:v>編集</x:v>
-      </x:c>
-      <x:c r="D18" s="155" t="str">
-        <x:v>SCR-016</x:v>
-      </x:c>
-      <x:c r="E18" s="155" t="str">
-        <x:v>taskId/version</x:v>
-      </x:c>
-      <x:c r="F18" s="155" t="str">
-        <x:v>管理者/担当PM</x:v>
-      </x:c>
-      <x:c r="G18" s="155" t="str">
-        <x:v>詳細へ</x:v>
-      </x:c>
-      <x:c r="H18" s="155"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="155" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B19" s="155" t="str">
-        <x:v>SCR-018</x:v>
-      </x:c>
-      <x:c r="C19" s="155" t="str">
-        <x:v>カード選択</x:v>
-      </x:c>
-      <x:c r="D19" s="155" t="str">
-        <x:v>SCR-017</x:v>
-      </x:c>
-      <x:c r="E19" s="155" t="str">
-        <x:v>taskId</x:v>
-      </x:c>
-      <x:c r="F19" s="155" t="str">
-        <x:v>関係者</x:v>
-      </x:c>
-      <x:c r="G19" s="155" t="str">
-        <x:v>看板へ</x:v>
-      </x:c>
-      <x:c r="H19" s="155"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="155" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B20" s="155" t="str">
-        <x:v>SCR-019</x:v>
-      </x:c>
-      <x:c r="C20" s="155" t="str">
-        <x:v>新規/編集</x:v>
-      </x:c>
-      <x:c r="D20" s="155" t="str">
-        <x:v>SCR-020</x:v>
-      </x:c>
-      <x:c r="E20" s="155" t="str">
-        <x:v>reportId/date</x:v>
-      </x:c>
-      <x:c r="F20" s="155" t="str">
-        <x:v>本人</x:v>
-      </x:c>
-      <x:c r="G20" s="155" t="str">
-        <x:v>一覧へ</x:v>
-      </x:c>
-      <x:c r="H20" s="155"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="155" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B21" s="155" t="str">
-        <x:v>SCR-002</x:v>
-      </x:c>
-      <x:c r="C21" s="155" t="str">
-        <x:v>通知アイコン</x:v>
-      </x:c>
-      <x:c r="D21" s="155" t="str">
-        <x:v>SCR-022</x:v>
-      </x:c>
-      <x:c r="E21" s="155" t="str">
-        <x:v>なし</x:v>
-      </x:c>
-      <x:c r="F21" s="155" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="G21" s="155" t="str">
+      <x:c r="F46" s="358" t="str">
+        <x:v>02／10_メニュー権限・11_機能権限参照</x:v>
+      </x:c>
+      <x:c r="G46" s="358" t="str">
         <x:v>元画面へ</x:v>
       </x:c>
-      <x:c r="H21" s="155"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="155" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B22" s="155" t="str">
-        <x:v>共通ユーザーMenu</x:v>
-      </x:c>
-      <x:c r="C22" s="155" t="str">
-        <x:v>Password変更</x:v>
-      </x:c>
-      <x:c r="D22" s="155" t="str">
-        <x:v>SCR-026</x:v>
-      </x:c>
-      <x:c r="E22" s="155" t="str">
-        <x:v>なし</x:v>
-      </x:c>
-      <x:c r="F22" s="155" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="G22" s="155" t="str">
-        <x:v>元画面へ</x:v>
-      </x:c>
-      <x:c r="H22" s="155"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="155" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B23" s="155" t="str">
-        <x:v>任意画面</x:v>
-      </x:c>
-      <x:c r="C23" s="155" t="str">
-        <x:v>Token期限切れ</x:v>
-      </x:c>
-      <x:c r="D23" s="155" t="str">
-        <x:v>SCR-001</x:v>
-      </x:c>
-      <x:c r="E23" s="155" t="str">
-        <x:v>redirect URL</x:v>
-      </x:c>
-      <x:c r="F23" s="155" t="str">
-        <x:v>Refresh失敗</x:v>
-      </x:c>
-      <x:c r="G23" s="155" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="H23" s="155" t="str">
-        <x:v>MSG-E-005</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="155" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B24" s="155" t="str">
-        <x:v>共通Menu</x:v>
-      </x:c>
-      <x:c r="C24" s="155" t="str">
-        <x:v>部門管理</x:v>
-      </x:c>
-      <x:c r="D24" s="155" t="str">
-        <x:v>SCR-007</x:v>
-      </x:c>
-      <x:c r="E24" s="155" t="str">
-        <x:v>なし</x:v>
-      </x:c>
-      <x:c r="F24" s="155" t="str">
-        <x:v>ADMIN</x:v>
-      </x:c>
-      <x:c r="G24" s="155" t="str">
-        <x:v>元画面へ</x:v>
-      </x:c>
-      <x:c r="H24" s="155" t="str">
-        <x:v>Menu権限</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="155" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B25" s="155" t="str">
-        <x:v>共通Menu</x:v>
-      </x:c>
-      <x:c r="C25" s="155" t="str">
-        <x:v>Task一覧</x:v>
-      </x:c>
-      <x:c r="D25" s="155" t="str">
-        <x:v>SCR-013</x:v>
-      </x:c>
-      <x:c r="E25" s="155" t="str">
-        <x:v>なし</x:v>
-      </x:c>
-      <x:c r="F25" s="155" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="G25" s="155" t="str">
-        <x:v>元画面へ</x:v>
-      </x:c>
-      <x:c r="H25" s="155" t="str">
-        <x:v>Menu権限</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="155" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B26" s="155" t="str">
-        <x:v>共通Menu</x:v>
-      </x:c>
-      <x:c r="C26" s="155" t="str">
-        <x:v>マイTask</x:v>
-      </x:c>
-      <x:c r="D26" s="155" t="str">
-        <x:v>SCR-014</x:v>
-      </x:c>
-      <x:c r="E26" s="155" t="str">
-        <x:v>なし</x:v>
-      </x:c>
-      <x:c r="F26" s="155" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="G26" s="155" t="str">
-        <x:v>元画面へ</x:v>
-      </x:c>
-      <x:c r="H26" s="155" t="str">
-        <x:v>Menu権限</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="155" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B27" s="155" t="str">
-        <x:v>共通Menu</x:v>
-      </x:c>
-      <x:c r="C27" s="155" t="str">
-        <x:v>日報検索</x:v>
-      </x:c>
-      <x:c r="D27" s="155" t="str">
-        <x:v>SCR-021</x:v>
-      </x:c>
-      <x:c r="E27" s="155" t="str">
-        <x:v>なし</x:v>
-      </x:c>
-      <x:c r="F27" s="155" t="str">
-        <x:v>ADMIN/PM</x:v>
-      </x:c>
-      <x:c r="G27" s="155" t="str">
-        <x:v>元画面へ</x:v>
-      </x:c>
-      <x:c r="H27" s="155" t="str">
-        <x:v>Menu権限</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="155" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B28" s="155" t="str">
-        <x:v>共通Menu</x:v>
-      </x:c>
-      <x:c r="C28" s="155" t="str">
-        <x:v>User管理</x:v>
-      </x:c>
-      <x:c r="D28" s="155" t="str">
-        <x:v>SCR-023</x:v>
-      </x:c>
-      <x:c r="E28" s="155" t="str">
-        <x:v>なし</x:v>
-      </x:c>
-      <x:c r="F28" s="155" t="str">
-        <x:v>ADMIN</x:v>
-      </x:c>
-      <x:c r="G28" s="155" t="str">
-        <x:v>元画面へ</x:v>
-      </x:c>
-      <x:c r="H28" s="155" t="str">
-        <x:v>Menu権限</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="155" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B29" s="155" t="str">
-        <x:v>共通Menu</x:v>
-      </x:c>
-      <x:c r="C29" s="155" t="str">
-        <x:v>Role管理</x:v>
-      </x:c>
-      <x:c r="D29" s="155" t="str">
-        <x:v>SCR-024</x:v>
-      </x:c>
-      <x:c r="E29" s="155" t="str">
-        <x:v>なし</x:v>
-      </x:c>
-      <x:c r="F29" s="155" t="str">
-        <x:v>ADMIN</x:v>
-      </x:c>
-      <x:c r="G29" s="155" t="str">
-        <x:v>元画面へ</x:v>
-      </x:c>
-      <x:c r="H29" s="155" t="str">
-        <x:v>Menu権限</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="155" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B30" s="155" t="str">
-        <x:v>共通Menu</x:v>
-      </x:c>
-      <x:c r="C30" s="155" t="str">
-        <x:v>操作Log</x:v>
-      </x:c>
-      <x:c r="D30" s="155" t="str">
-        <x:v>SCR-025</x:v>
-      </x:c>
-      <x:c r="E30" s="155" t="str">
-        <x:v>なし</x:v>
-      </x:c>
-      <x:c r="F30" s="155" t="str">
-        <x:v>ADMIN</x:v>
-      </x:c>
-      <x:c r="G30" s="155" t="str">
-        <x:v>元画面へ</x:v>
-      </x:c>
-      <x:c r="H30" s="155" t="str">
-        <x:v>Menu権限</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="236" t="str">
-        <x:v>画面IDは省略せずSCR-xxxを完全記載する。Menu遷移はMenu権限と02_権限基本設計書を参照する。</x:v>
-      </x:c>
-      <x:c r="B32" s="236"/>
-      <x:c r="C32" s="236"/>
-      <x:c r="D32" s="236"/>
-      <x:c r="E32" s="236"/>
-      <x:c r="F32" s="236"/>
-      <x:c r="G32" s="236"/>
-      <x:c r="H32" s="236"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="236"/>
-      <x:c r="B33" s="236"/>
-      <x:c r="C33" s="236"/>
-      <x:c r="D33" s="236"/>
-      <x:c r="E33" s="236"/>
-      <x:c r="F33" s="236"/>
-      <x:c r="G33" s="236"/>
-      <x:c r="H33" s="236"/>
+      <x:c r="H46" s="358" t="str">
+        <x:v>遷移の正本：03_画面共通設計書／13_画面遷移。SCR-002固有機能ではない。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:H3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:H4"/>
-    <x:mergeCell ref="A6:H6"/>
-    <x:mergeCell ref="A32:H33"/>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A5:H5"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3525,6 +5045,12 @@
       <x:c r="D1" s="20"/>
       <x:c r="E1" s="20"/>
       <x:c r="F1" s="20"/>
+      <x:c r="G1"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="20"/>
@@ -3533,6 +5059,12 @@
       <x:c r="D2" s="20"/>
       <x:c r="E2" s="20"/>
       <x:c r="F2" s="20"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="23" t="str">
@@ -3543,30 +5075,50 @@
         <x:v>Company WorkHub</x:v>
       </x:c>
       <x:c r="D3" s="21"/>
-      <x:c r="E3" s="23" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="E3" s="359" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="F3" s="23"/>
-      <x:c r="G3" t="str">
-        <x:v>CW-BD-042</x:v>
-      </x:c>
+      <x:c r="G3" t="str"/>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="23" t="str">
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="23"/>
-      <x:c r="C4" s="21" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="C4" s="360" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="D4" s="21"/>
-      <x:c r="E4" s="23" t="str">
-        <x:v>作成日</x:v>
+      <x:c r="E4" s="359" t="str">
+        <x:v>作成日：2026-09-24</x:v>
       </x:c>
       <x:c r="F4" s="35"/>
-      <x:c r="G4" s="36" t="n">
-        <x:v>46239</x:v>
-      </x:c>
+      <x:c r="G4" s="36"/>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5"/>
+      <x:c r="B5"/>
+      <x:c r="C5"/>
+      <x:c r="D5"/>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="26" t="str">
@@ -3577,6 +5129,12 @@
       <x:c r="D6" s="26"/>
       <x:c r="E6" s="26"/>
       <x:c r="F6" s="26"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="31" t="str">
@@ -3597,6 +5155,12 @@
       <x:c r="F7" s="31" t="str">
         <x:v>備考</x:v>
       </x:c>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="33" t="str">
@@ -3614,7 +5178,13 @@
       <x:c r="E8" s="33" t="str">
         <x:v>通信失敗時MSG-E-007</x:v>
       </x:c>
-      <x:c r="F8" s="33" t="str"/>
+      <x:c r="F8" s="33"/>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="33" t="str">
@@ -3632,7 +5202,13 @@
       <x:c r="E9" s="33" t="str">
         <x:v>権限取得失敗時安全側で非表示</x:v>
       </x:c>
-      <x:c r="F9" s="33" t="str"/>
+      <x:c r="F9" s="33"/>
+      <x:c r="G9"/>
+      <x:c r="H9"/>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="33" t="str">
@@ -3650,7 +5226,13 @@
       <x:c r="E10" s="33" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="F10" s="33" t="str"/>
+      <x:c r="F10" s="33"/>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="33" t="str">
@@ -3668,7 +5250,13 @@
       <x:c r="E11" s="33" t="str">
         <x:v>共通Error表示</x:v>
       </x:c>
-      <x:c r="F11" s="33" t="str"/>
+      <x:c r="F11" s="33"/>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="33" t="str">
@@ -3686,81 +5274,115 @@
       <x:c r="E12" s="33" t="str">
         <x:v>入力不正を項目下表示</x:v>
       </x:c>
-      <x:c r="F12" s="33" t="str"/>
+      <x:c r="F12" s="33"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="33" t="str">
         <x:v>新規/編集/削除</x:v>
       </x:c>
       <x:c r="B13" s="33" t="str">
-        <x:v>画面遷移またはDialog</x:v>
+        <x:v>新規/編集/退職/停止/削除</x:v>
       </x:c>
       <x:c r="C13" s="33" t="str">
-        <x:v>確認後API呼出</x:v>
+        <x:v>画面遷移または確認Dialog。退職・停止・削除は業務条件確認後実行</x:v>
       </x:c>
       <x:c r="D13" s="33" t="str">
-        <x:v>更新権限</x:v>
+        <x:v>更新Permissionと対象状態</x:v>
       </x:c>
       <x:c r="E13" s="33" t="str">
-        <x:v>API Error表示</x:v>
+        <x:v>業務固有Messageを表示し元状態を保持</x:v>
       </x:c>
       <x:c r="F13" s="33" t="str">
         <x:v>二重送信防止</x:v>
       </x:c>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="33" t="str">
         <x:v>保存/取消/戻る</x:v>
       </x:c>
       <x:c r="B14" s="33" t="str">
-        <x:v>入力保存、破棄、前画面復帰</x:v>
+        <x:v>保存/取消/戻る</x:v>
       </x:c>
       <x:c r="C14" s="33" t="str">
-        <x:v>未保存時確認</x:v>
+        <x:v>取消/戻るは呼出元へ復帰。入力変更ありの場合は破棄確認</x:v>
       </x:c>
       <x:c r="D14" s="33" t="str">
         <x:v>更新権限</x:v>
       </x:c>
       <x:c r="E14" s="33" t="str">
-        <x:v>保存失敗時入力保持</x:v>
-      </x:c>
-      <x:c r="F14" s="33" t="str"/>
+        <x:v>保存失敗時は入力と選択状態を保持</x:v>
+      </x:c>
+      <x:c r="F14" s="33" t="str">
+        <x:v>遷移元検索条件・Pageを保持</x:v>
+      </x:c>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="33" t="str">
         <x:v>Import/Export</x:v>
       </x:c>
       <x:c r="B15" s="33" t="str">
-        <x:v>Excel Upload/Download</x:v>
+        <x:v>Import/Export</x:v>
       </x:c>
       <x:c r="C15" s="33" t="str">
-        <x:v>進捗・結果表示</x:v>
+        <x:v>Importは結果件数・行別Error・一時Passwordを一回表示。Exportは現在条件の全対象</x:v>
       </x:c>
       <x:c r="D15" s="33" t="str">
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E15" s="33" t="str">
-        <x:v>部分失敗明細</x:v>
-      </x:c>
-      <x:c r="F15" s="33" t="str"/>
+        <x:v>部分失敗明細。0件ExportはFileを生成しない</x:v>
+      </x:c>
+      <x:c r="F15" s="33" t="str">
+        <x:v>Import最大1000行、Export最大50000件</x:v>
+      </x:c>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="33" t="str">
         <x:v>Paging/Sort</x:v>
       </x:c>
       <x:c r="B16" s="33" t="str">
-        <x:v>20/50/100、既定20、列Sort</x:v>
+        <x:v>Paging/Sort</x:v>
       </x:c>
       <x:c r="C16" s="33" t="str">
-        <x:v>条件を保持して再取得</x:v>
+        <x:v>20/50/100、既定20。検索・詳細往復時に条件/Page/Sortを保持</x:v>
       </x:c>
       <x:c r="D16" s="33" t="str">
         <x:v>参照範囲</x:v>
       </x:c>
       <x:c r="E16" s="33" t="str">
-        <x:v>-</x:v>
+        <x:v>0件は空一覧と対象なし表示</x:v>
       </x:c>
       <x:c r="F16" s="33" t="str"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="33" t="str">
@@ -3791,9 +5413,8 @@
     <x:mergeCell ref="F3:G3"/>
     <x:mergeCell ref="A4:B4"/>
     <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="F4:G4"/>
     <x:mergeCell ref="A6:F6"/>
+    <x:mergeCell ref="E4:G4"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3810,6 +5431,7 @@
     <x:col min="5" max="5" width="52" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -3822,6 +5444,11 @@
       <x:c r="E1" s="20"/>
       <x:c r="F1" s="20"/>
       <x:c r="G1" s="20"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="20"/>
@@ -3831,6 +5458,11 @@
       <x:c r="E2" s="20"/>
       <x:c r="F2" s="20"/>
       <x:c r="G2" s="20"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="23" t="str">
@@ -3841,30 +5473,54 @@
         <x:v>Company WorkHub</x:v>
       </x:c>
       <x:c r="D3" s="21"/>
-      <x:c r="E3" s="23" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="E3" s="359" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="F3" s="23"/>
       <x:c r="G3" s="21" t="str">
         <x:v>CW-BD-044</x:v>
       </x:c>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="23" t="str">
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="23"/>
-      <x:c r="C4" s="21" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="C4" s="360" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="D4" s="21"/>
       <x:c r="E4" s="23" t="str">
         <x:v>作成日</x:v>
       </x:c>
       <x:c r="F4" s="23"/>
-      <x:c r="G4" s="24" t="n">
-        <x:v>46239</x:v>
-      </x:c>
+      <x:c r="G4" s="361" t="str">
+        <x:v>2026-09-24</x:v>
+      </x:c>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5"/>
+      <x:c r="B5"/>
+      <x:c r="C5"/>
+      <x:c r="D5"/>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="26" t="str">
@@ -3876,6 +5532,11 @@
       <x:c r="E6" s="26"/>
       <x:c r="F6" s="26"/>
       <x:c r="G6" s="26"/>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="31" t="str">
@@ -3891,7 +5552,7 @@
         <x:v>規則</x:v>
       </x:c>
       <x:c r="E7" s="31" t="str">
-        <x:v>メッセージ例</x:v>
+        <x:v>Message ID</x:v>
       </x:c>
       <x:c r="F7" s="31" t="str">
         <x:v>実施箇所</x:v>
@@ -3899,6 +5560,13 @@
       <x:c r="G7" s="31" t="str">
         <x:v>備考</x:v>
       </x:c>
+      <x:c r="H7" s="339" t="str">
+        <x:v>Message Parameter</x:v>
+      </x:c>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="33" t="str">
@@ -3914,7 +5582,7 @@
         <x:v>null/空文字/空白のみ不可</x:v>
       </x:c>
       <x:c r="E8" s="33" t="str">
-        <x:v>入力してください。</x:v>
+        <x:v>MSG-V-001</x:v>
       </x:c>
       <x:c r="F8" s="33" t="str">
         <x:v>フロントエンド/バックエンド</x:v>
@@ -3922,6 +5590,13 @@
       <x:c r="G8" s="33" t="str">
         <x:v>バックエンド最終</x:v>
       </x:c>
+      <x:c r="H8" s="339" t="str">
+        <x:v>[画面項目名]</x:v>
+      </x:c>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="33" t="str">
@@ -3937,14 +5612,21 @@
         <x:v>定義桁数以下</x:v>
       </x:c>
       <x:c r="E9" s="33" t="str">
-        <x:v>{項目}は{max}文字以内で入力してください。</x:v>
+        <x:v>MSG-V-002</x:v>
       </x:c>
       <x:c r="F9" s="33" t="str">
         <x:v>フロントエンド/バックエンド</x:v>
       </x:c>
       <x:c r="G9" s="33" t="str">
-        <x:v>Unicode文字数定義を統一</x:v>
-      </x:c>
+        <x:v>Unicode Code Point数定義を統一</x:v>
+      </x:c>
+      <x:c r="H9" s="339" t="str">
+        <x:v>[画面項目名, 最大Code Point数]</x:v>
+      </x:c>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="33" t="str">
@@ -3960,12 +5642,19 @@
         <x:v>標準メール形式</x:v>
       </x:c>
       <x:c r="E10" s="33" t="str">
-        <x:v>正しいメールアドレスを入力してください。</x:v>
+        <x:v>MSG-V-003</x:v>
       </x:c>
       <x:c r="F10" s="33" t="str">
         <x:v>フロントエンド/バックエンド</x:v>
       </x:c>
-      <x:c r="G10" s="33" t="str"/>
+      <x:c r="G10" s="33"/>
+      <x:c r="H10" s="339" t="str">
+        <x:v>[画面項目名]</x:v>
+      </x:c>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="33" t="str">
@@ -3981,12 +5670,19 @@
         <x:v>yyyy-MM-ddで実在日</x:v>
       </x:c>
       <x:c r="E11" s="33" t="str">
-        <x:v>正しい日付を入力してください。</x:v>
+        <x:v>MSG-V-004</x:v>
       </x:c>
       <x:c r="F11" s="33" t="str">
         <x:v>フロントエンド/バックエンド</x:v>
       </x:c>
-      <x:c r="G11" s="33" t="str"/>
+      <x:c r="G11" s="33"/>
+      <x:c r="H11" s="339" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="33" t="str">
@@ -4002,12 +5698,19 @@
         <x:v>開始日&lt;=終了日</x:v>
       </x:c>
       <x:c r="E12" s="33" t="str">
-        <x:v>開始日は終了日以前にしてください。</x:v>
+        <x:v>MSG-V-005</x:v>
       </x:c>
       <x:c r="F12" s="33" t="str">
         <x:v>フロントエンド/バックエンド</x:v>
       </x:c>
-      <x:c r="G12" s="33" t="str"/>
+      <x:c r="G12" s="33"/>
+      <x:c r="H12" s="339" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="33" t="str">
@@ -4023,12 +5726,19 @@
         <x:v>0&lt;=値、日報は0&lt;値&lt;=24</x:v>
       </x:c>
       <x:c r="E13" s="33" t="str">
-        <x:v>作業時間は0より大きく24以下で入力してください。</x:v>
+        <x:v>MSG-V-006</x:v>
       </x:c>
       <x:c r="F13" s="33" t="str">
         <x:v>フロントエンド/バックエンド</x:v>
       </x:c>
-      <x:c r="G13" s="33" t="str"/>
+      <x:c r="G13" s="33"/>
+      <x:c r="H13" s="339" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="33" t="str">
@@ -4044,12 +5754,19 @@
         <x:v>論理削除を含む一意方針に従う</x:v>
       </x:c>
       <x:c r="E14" s="33" t="str">
-        <x:v>既に使用されています。</x:v>
+        <x:v>MSG-V-007</x:v>
       </x:c>
       <x:c r="F14" s="33" t="str">
         <x:v>バックエンド/DB</x:v>
       </x:c>
-      <x:c r="G14" s="33" t="str"/>
+      <x:c r="G14" s="33"/>
+      <x:c r="H14" s="339" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="33" t="str">
@@ -4065,12 +5782,19 @@
         <x:v>対象が存在し有効</x:v>
       </x:c>
       <x:c r="E15" s="33" t="str">
-        <x:v>指定データが存在しません。</x:v>
+        <x:v>MSG-V-008</x:v>
       </x:c>
       <x:c r="F15" s="33" t="str">
         <x:v>バックエンド</x:v>
       </x:c>
-      <x:c r="G15" s="33" t="str"/>
+      <x:c r="G15" s="33"/>
+      <x:c r="H15" s="339" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="33" t="str">
@@ -4086,7 +5810,7 @@
         <x:v>Role + データ範囲</x:v>
       </x:c>
       <x:c r="E16" s="33" t="str">
-        <x:v>権限がありません。</x:v>
+        <x:v>MSG-V-009</x:v>
       </x:c>
       <x:c r="F16" s="33" t="str">
         <x:v>バックエンド</x:v>
@@ -4094,6 +5818,13 @@
       <x:c r="G16" s="33" t="str">
         <x:v>フロントエンドは表示制御</x:v>
       </x:c>
+      <x:c r="H16" s="339" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="33" t="str">
@@ -4109,12 +5840,15 @@
         <x:v>要求Version=DB Version</x:v>
       </x:c>
       <x:c r="E17" s="33" t="str">
-        <x:v>他ユーザーに更新されています。</x:v>
+        <x:v>MSG-V-010</x:v>
       </x:c>
       <x:c r="F17" s="33" t="str">
         <x:v>バックエンド/DB</x:v>
       </x:c>
       <x:c r="G17" s="33" t="str"/>
+      <x:c r="H17" s="339" t="str">
+        <x:v>なし</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="33" t="str">
@@ -4130,12 +5864,15 @@
         <x:v>8～64、大文字/小文字/数字/特殊文字、User名/現Passwordと不同</x:v>
       </x:c>
       <x:c r="E18" s="33" t="str">
-        <x:v>パスワード規則を満たしていません。</x:v>
+        <x:v>MSG-V-011</x:v>
       </x:c>
       <x:c r="F18" s="33" t="str">
         <x:v>フロントエンド/バックエンド</x:v>
       </x:c>
       <x:c r="G18" s="33" t="str"/>
+      <x:c r="H18" s="339" t="str">
+        <x:v>なし</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="33" t="str">
@@ -4151,13 +5888,16 @@
         <x:v>許可拡張子+MIME、10MB以下、20件以下、名前255</x:v>
       </x:c>
       <x:c r="E19" s="33" t="str">
-        <x:v>ファイルを確認してください。</x:v>
+        <x:v>MSG-V-012</x:v>
       </x:c>
       <x:c r="F19" s="33" t="str">
         <x:v>フロントエンド/バックエンド</x:v>
       </x:c>
       <x:c r="G19" s="33" t="str">
         <x:v>実行/Script禁止</x:v>
+      </x:c>
+      <x:c r="H19" s="339" t="str">
+        <x:v>なし</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -4174,12 +5914,15 @@
         <x:v>状態遷移表に存在する遷移のみ</x:v>
       </x:c>
       <x:c r="E20" s="33" t="str">
-        <x:v>状態を変更できません。</x:v>
+        <x:v>MSG-V-013</x:v>
       </x:c>
       <x:c r="F20" s="33" t="str">
         <x:v>バックエンド</x:v>
       </x:c>
       <x:c r="G20" s="33" t="str"/>
+      <x:c r="H20" s="339" t="str">
+        <x:v>なし</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="33" t="str">
@@ -4189,18 +5932,21 @@
         <x:v>日報重複</x:v>
       </x:c>
       <x:c r="C21" s="33" t="str">
-        <x:v>社員+日付</x:v>
+        <x:v>社員＋PJ＋日付</x:v>
       </x:c>
       <x:c r="D21" s="33" t="str">
-        <x:v>一日一件</x:v>
+        <x:v>同一社員・同一PJ・同一日一件</x:v>
       </x:c>
       <x:c r="E21" s="33" t="str">
-        <x:v>当日の日報は登録済みです。</x:v>
+        <x:v>MSG-V-014</x:v>
       </x:c>
       <x:c r="F21" s="33" t="str">
         <x:v>バックエンド/DB</x:v>
       </x:c>
       <x:c r="G21" s="33" t="str"/>
+      <x:c r="H21" s="339" t="str">
+        <x:v>なし</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="33" t="str">
@@ -4216,12 +5962,175 @@
         <x:v>数字とハイフン、20桁以内</x:v>
       </x:c>
       <x:c r="E22" s="33" t="str">
-        <x:v>電話番号形式を確認してください。</x:v>
+        <x:v>MSG-V-015</x:v>
       </x:c>
       <x:c r="F22" s="33" t="str">
         <x:v>フロントエンド/バックエンド</x:v>
       </x:c>
       <x:c r="G22" s="33" t="str"/>
+      <x:c r="H22" s="339" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="339" t="str">
+        <x:v>VAL-016</x:v>
+      </x:c>
+      <x:c r="B23" s="339" t="str">
+        <x:v>退職日</x:v>
+      </x:c>
+      <x:c r="C23" s="339" t="str">
+        <x:v>leftDate</x:v>
+      </x:c>
+      <x:c r="D23" s="339" t="str">
+        <x:v>入社日&lt;=退職日&lt;=System日付。退職時必須</x:v>
+      </x:c>
+      <x:c r="E23" s="339" t="str">
+        <x:v>MSG-V-016</x:v>
+      </x:c>
+      <x:c r="F23" s="339" t="str">
+        <x:v>フロントエンド/バックエンド</x:v>
+      </x:c>
+      <x:c r="G23" s="339" t="str">
+        <x:v>未来日不可</x:v>
+      </x:c>
+      <x:c r="H23" s="339" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="339" t="str">
+        <x:v>VAL-017</x:v>
+      </x:c>
+      <x:c r="B24" s="339" t="str">
+        <x:v>上司</x:v>
+      </x:c>
+      <x:c r="C24" s="339" t="str">
+        <x:v>managerId</x:v>
+      </x:c>
+      <x:c r="D24" s="339" t="str">
+        <x:v>在籍社員、本人以外、上司関係が循環しない</x:v>
+      </x:c>
+      <x:c r="E24" s="339" t="str">
+        <x:v>MSG-V-017</x:v>
+      </x:c>
+      <x:c r="F24" s="339" t="str">
+        <x:v>バックエンド</x:v>
+      </x:c>
+      <x:c r="G24" s="339" t="str">
+        <x:v>未指定可</x:v>
+      </x:c>
+      <x:c r="H24" s="339" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="54" customHeight="1">
+      <x:c r="A25" s="344" t="str">
+        <x:v>VAL-018</x:v>
+      </x:c>
+      <x:c r="B25" s="344" t="str">
+        <x:v>Role</x:v>
+      </x:c>
+      <x:c r="C25" s="344" t="str">
+        <x:v>roleIds</x:v>
+      </x:c>
+      <x:c r="D25" s="344" t="str">
+        <x:v>有効Roleのみ、重複不可。ROLE-ADMIN/ROLE-PM/ROLE-EMPのいずれか1つ以上を含む。</x:v>
+      </x:c>
+      <x:c r="E25" s="344" t="str">
+        <x:v>MSG-V-018</x:v>
+      </x:c>
+      <x:c r="F25" s="344" t="str">
+        <x:v>フロントエンド/バックエンド</x:v>
+      </x:c>
+      <x:c r="G25" s="344" t="str">
+        <x:v>初期値ROLE-EMP</x:v>
+      </x:c>
+      <x:c r="H25" s="344" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+      <x:c r="I25" s="344"/>
+      <x:c r="J25" s="344"/>
+      <x:c r="K25" s="344"/>
+      <x:c r="L25" s="344"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="339" t="str">
+        <x:v>VAL-019</x:v>
+      </x:c>
+      <x:c r="B26" s="339" t="str">
+        <x:v>部門名</x:v>
+      </x:c>
+      <x:c r="C26" s="339" t="str">
+        <x:v>departmentName</x:v>
+      </x:c>
+      <x:c r="D26" s="339" t="str">
+        <x:v>Trim後、同一親部門内で完全一致重複不可。論理削除済を含む</x:v>
+      </x:c>
+      <x:c r="E26" s="339" t="str">
+        <x:v>MSG-V-019</x:v>
+      </x:c>
+      <x:c r="F26" s="339" t="str">
+        <x:v>バックエンド/DB</x:v>
+      </x:c>
+      <x:c r="G26" s="339" t="str">
+        <x:v>RootはparentId=nullを同一親として扱う</x:v>
+      </x:c>
+      <x:c r="H26" s="339" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="339" t="str">
+        <x:v>VAL-020</x:v>
+      </x:c>
+      <x:c r="B27" s="339" t="str">
+        <x:v>退職引継</x:v>
+      </x:c>
+      <x:c r="C27" s="339" t="str">
+        <x:v>reassignmentAssigneeId</x:v>
+      </x:c>
+      <x:c r="D27" s="339" t="str">
+        <x:v>REASSIGN時、全対象TaskのPJに参加する在籍社員で本人以外</x:v>
+      </x:c>
+      <x:c r="E27" s="339" t="str">
+        <x:v>MSG-V-020</x:v>
+      </x:c>
+      <x:c r="F27" s="339" t="str">
+        <x:v>バックエンド</x:v>
+      </x:c>
+      <x:c r="G27" s="339" t="str">
+        <x:v>未完了Taskが0件の場合は不要</x:v>
+      </x:c>
+      <x:c r="H27" s="339" t="str">
+        <x:v>なし</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>VAL-021</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>入社日</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>joinedDate</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>社員登録・Excel取込では実在日かつSystem日付以下</x:v>
+      </x:c>
+      <x:c r="E28" s="339" t="str">
+        <x:v>MSG-V-021</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>フロントエンド/バックエンド</x:v>
+      </x:c>
+      <x:c r="G28" t="str">
+        <x:v>入社予定状態は第1期対象外</x:v>
+      </x:c>
+      <x:c r="H28" s="339" t="str">
+        <x:v>なし</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -4242,8 +6151,8 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="9" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="9" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="9" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="9" hidden="0" customWidth="1"/>
@@ -4261,1567 +6170,588 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
-      <x:c r="A1" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="B1" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="C1" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="D1" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="E1" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="F1" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="G1" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="H1" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="I1" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="J1" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="K1" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="L1" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="M1" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="N1" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="O1" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="P1" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
+      <x:c r="A1" s="354" t="str">
+        <x:v>18_WF作成規約</x:v>
+      </x:c>
+      <x:c r="B1" s="353"/>
+      <x:c r="C1"/>
+      <x:c r="D1"/>
+      <x:c r="E1"/>
+      <x:c r="F1"/>
+      <x:c r="G1"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
+      <x:c r="M1"/>
+      <x:c r="N1"/>
+      <x:c r="O1"/>
+      <x:c r="P1"/>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="B2" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="C2" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="D2" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="E2" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="F2" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="G2" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="H2" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="I2" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="J2" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="K2" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="L2" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="M2" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="N2" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="O2" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
-      <x:c r="P2" s="52" t="str">
-        <x:v>画面ワイヤーフレーム作成規約</x:v>
-      </x:c>
+      <x:c r="A2" s="353"/>
+      <x:c r="B2" s="353"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
+      <x:c r="M2"/>
+      <x:c r="N2"/>
+      <x:c r="O2"/>
+      <x:c r="P2"/>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="48"/>
-      <x:c r="B3" s="48"/>
-      <x:c r="C3" s="48"/>
-      <x:c r="D3" s="48"/>
-      <x:c r="E3" s="48"/>
-      <x:c r="F3" s="48"/>
-      <x:c r="G3" s="48"/>
-      <x:c r="H3" s="48"/>
-      <x:c r="I3" s="48"/>
-      <x:c r="J3" s="48"/>
-      <x:c r="K3" s="48"/>
-      <x:c r="L3" s="48"/>
-      <x:c r="M3" s="48"/>
-      <x:c r="N3" s="48"/>
-      <x:c r="O3" s="48"/>
-      <x:c r="P3" s="48"/>
+      <x:c r="A3" s="353" t="str">
+        <x:v>Company WorkHub</x:v>
+      </x:c>
+      <x:c r="B3" s="353"/>
+      <x:c r="C3"/>
+      <x:c r="D3"/>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
+      <x:c r="M3"/>
+      <x:c r="N3"/>
+      <x:c r="O3"/>
+      <x:c r="P3"/>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="54" t="str">
-        <x:v>1. ワイヤーフレームの読み方</x:v>
-      </x:c>
-      <x:c r="B4" s="54" t="str">
-        <x:v>1. ワイヤーフレームの読み方</x:v>
-      </x:c>
-      <x:c r="C4" s="54" t="str">
-        <x:v>1. ワイヤーフレームの読み方</x:v>
-      </x:c>
-      <x:c r="D4" s="54" t="str">
-        <x:v>1. ワイヤーフレームの読み方</x:v>
-      </x:c>
-      <x:c r="E4" s="54" t="str">
-        <x:v>1. ワイヤーフレームの読み方</x:v>
-      </x:c>
-      <x:c r="F4" s="54" t="str">
-        <x:v>1. ワイヤーフレームの読み方</x:v>
-      </x:c>
-      <x:c r="G4" s="54" t="str">
-        <x:v>1. ワイヤーフレームの読み方</x:v>
-      </x:c>
-      <x:c r="H4" s="54" t="str">
-        <x:v>1. ワイヤーフレームの読み方</x:v>
-      </x:c>
-      <x:c r="I4" s="54" t="str">
-        <x:v>1. ワイヤーフレームの読み方</x:v>
-      </x:c>
-      <x:c r="J4" s="54" t="str">
-        <x:v>1. ワイヤーフレームの読み方</x:v>
-      </x:c>
-      <x:c r="K4" s="54" t="str">
-        <x:v>1. ワイヤーフレームの読み方</x:v>
-      </x:c>
-      <x:c r="L4" s="54" t="str">
-        <x:v>1. ワイヤーフレームの読み方</x:v>
-      </x:c>
-      <x:c r="M4" s="54" t="str">
-        <x:v>1. ワイヤーフレームの読み方</x:v>
-      </x:c>
-      <x:c r="N4" s="54" t="str">
-        <x:v>1. ワイヤーフレームの読み方</x:v>
-      </x:c>
-      <x:c r="O4" s="54" t="str">
-        <x:v>1. ワイヤーフレームの読み方</x:v>
-      </x:c>
-      <x:c r="P4" s="54" t="str">
-        <x:v>1. ワイヤーフレームの読み方</x:v>
-      </x:c>
+      <x:c r="A4" s="353"/>
+      <x:c r="B4" s="353"/>
+      <x:c r="C4"/>
+      <x:c r="D4"/>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
+      <x:c r="M4"/>
+      <x:c r="N4"/>
+      <x:c r="O4"/>
+      <x:c r="P4"/>
     </x:row>
     <x:row r="5" ht="22" customHeight="1">
-      <x:c r="A5" s="48"/>
-      <x:c r="B5" s="48"/>
-      <x:c r="C5" s="48"/>
-      <x:c r="D5" s="48"/>
-      <x:c r="E5" s="48"/>
-      <x:c r="F5" s="48"/>
-      <x:c r="G5" s="48"/>
-      <x:c r="H5" s="48"/>
-      <x:c r="I5" s="48"/>
-      <x:c r="J5" s="48"/>
-      <x:c r="K5" s="48"/>
-      <x:c r="L5" s="48"/>
-      <x:c r="M5" s="48"/>
-      <x:c r="N5" s="48"/>
-      <x:c r="O5" s="48"/>
-      <x:c r="P5" s="48"/>
+      <x:c r="A5" s="353" t="str">
+        <x:v>BL-2026-09-24 / Review中</x:v>
+      </x:c>
+      <x:c r="B5" s="353"/>
+      <x:c r="C5"/>
+      <x:c r="D5"/>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
+      <x:c r="M5"/>
+      <x:c r="N5"/>
+      <x:c r="O5"/>
+      <x:c r="P5"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="59" t="str">
-        <x:v>番号</x:v>
-      </x:c>
-      <x:c r="B6" s="59" t="str">
-        <x:v>番号</x:v>
-      </x:c>
-      <x:c r="C6" s="59" t="str">
-        <x:v>番号</x:v>
-      </x:c>
-      <x:c r="D6" s="59" t="str">
-        <x:v>番号</x:v>
-      </x:c>
-      <x:c r="E6" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-      <x:c r="F6" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-      <x:c r="G6" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-      <x:c r="H6" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-      <x:c r="I6" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-      <x:c r="J6" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-      <x:c r="K6" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-      <x:c r="L6" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-      <x:c r="M6" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-      <x:c r="N6" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-      <x:c r="O6" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-      <x:c r="P6" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="59" t="str">
-        <x:v>番号</x:v>
-      </x:c>
-      <x:c r="B7" s="59" t="str">
-        <x:v>番号</x:v>
-      </x:c>
-      <x:c r="C7" s="59" t="str">
-        <x:v>番号</x:v>
-      </x:c>
-      <x:c r="D7" s="59" t="str">
-        <x:v>番号</x:v>
-      </x:c>
-      <x:c r="E7" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-      <x:c r="F7" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-      <x:c r="G7" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-      <x:c r="H7" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-      <x:c r="I7" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-      <x:c r="J7" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-      <x:c r="K7" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-      <x:c r="L7" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-      <x:c r="M7" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-      <x:c r="N7" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-      <x:c r="O7" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-      <x:c r="P7" s="63" t="str">
-        <x:v>画面項目定義SheetのNo.と対応する</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="22" customHeight="1">
-      <x:c r="A8" s="59" t="str">
+      <x:c r="A6" s="353"/>
+      <x:c r="B6" s="353"/>
+      <x:c r="C6"/>
+      <x:c r="D6"/>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
+      <x:c r="M6"/>
+      <x:c r="N6"/>
+      <x:c r="O6"/>
+      <x:c r="P6"/>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
+      <x:c r="A7" s="356" t="str">
+        <x:v>記号・領域</x:v>
+      </x:c>
+      <x:c r="B7" s="356" t="str">
+        <x:v>意味</x:v>
+      </x:c>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
+      <x:c r="M7"/>
+      <x:c r="N7"/>
+      <x:c r="O7"/>
+      <x:c r="P7"/>
+    </x:row>
+    <x:row r="8" ht="36" customHeight="1">
+      <x:c r="A8" s="358" t="str">
         <x:v>*</x:v>
       </x:c>
-      <x:c r="B8" s="59" t="str">
-        <x:v>*</x:v>
-      </x:c>
-      <x:c r="C8" s="59" t="str">
-        <x:v>*</x:v>
-      </x:c>
-      <x:c r="D8" s="59" t="str">
-        <x:v>*</x:v>
-      </x:c>
-      <x:c r="E8" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-      <x:c r="F8" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-      <x:c r="G8" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-      <x:c r="H8" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-      <x:c r="I8" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-      <x:c r="J8" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-      <x:c r="K8" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-      <x:c r="L8" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-      <x:c r="M8" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-      <x:c r="N8" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-      <x:c r="O8" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-      <x:c r="P8" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="22" customHeight="1">
-      <x:c r="A9" s="59" t="str">
-        <x:v>*</x:v>
-      </x:c>
-      <x:c r="B9" s="59" t="str">
-        <x:v>*</x:v>
-      </x:c>
-      <x:c r="C9" s="59" t="str">
-        <x:v>*</x:v>
-      </x:c>
-      <x:c r="D9" s="59" t="str">
-        <x:v>*</x:v>
-      </x:c>
-      <x:c r="E9" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-      <x:c r="F9" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-      <x:c r="G9" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-      <x:c r="H9" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-      <x:c r="I9" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-      <x:c r="J9" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-      <x:c r="K9" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-      <x:c r="L9" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-      <x:c r="M9" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-      <x:c r="N9" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-      <x:c r="O9" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-      <x:c r="P9" s="63" t="str">
-        <x:v>必須入力項目を示す</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="59" t="str">
+      <x:c r="B8" s="358" t="str">
+        <x:v>必須入力項目</x:v>
+      </x:c>
+      <x:c r="C8"/>
+      <x:c r="D8"/>
+      <x:c r="E8"/>
+      <x:c r="F8"/>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
+      <x:c r="M8"/>
+      <x:c r="N8"/>
+      <x:c r="O8"/>
+      <x:c r="P8"/>
+    </x:row>
+    <x:row r="9" ht="36" customHeight="1">
+      <x:c r="A9" s="357" t="str">
         <x:v>白色枠</x:v>
       </x:c>
-      <x:c r="B10" s="59" t="str">
-        <x:v>白色枠</x:v>
-      </x:c>
-      <x:c r="C10" s="59" t="str">
-        <x:v>白色枠</x:v>
-      </x:c>
-      <x:c r="D10" s="59" t="str">
-        <x:v>白色枠</x:v>
-      </x:c>
-      <x:c r="E10" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-      <x:c r="F10" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-      <x:c r="G10" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-      <x:c r="H10" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-      <x:c r="I10" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-      <x:c r="J10" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-      <x:c r="K10" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-      <x:c r="L10" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-      <x:c r="M10" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-      <x:c r="N10" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-      <x:c r="O10" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-      <x:c r="P10" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="22" customHeight="1">
-      <x:c r="A11" s="59" t="str">
-        <x:v>白色枠</x:v>
-      </x:c>
-      <x:c r="B11" s="59" t="str">
-        <x:v>白色枠</x:v>
-      </x:c>
-      <x:c r="C11" s="59" t="str">
-        <x:v>白色枠</x:v>
-      </x:c>
-      <x:c r="D11" s="59" t="str">
-        <x:v>白色枠</x:v>
-      </x:c>
-      <x:c r="E11" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-      <x:c r="F11" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-      <x:c r="G11" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-      <x:c r="H11" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-      <x:c r="I11" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-      <x:c r="J11" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-      <x:c r="K11" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-      <x:c r="L11" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-      <x:c r="M11" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-      <x:c r="N11" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-      <x:c r="O11" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-      <x:c r="P11" s="63" t="str">
-        <x:v>入力、選択、または参照値の表示領域</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="67" t="str">
+      <x:c r="B9" s="357" t="str">
+        <x:v>入力、選択、参照値の表示領域</x:v>
+      </x:c>
+      <x:c r="C9"/>
+      <x:c r="D9"/>
+      <x:c r="E9"/>
+      <x:c r="F9"/>
+      <x:c r="G9"/>
+      <x:c r="H9"/>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
+      <x:c r="M9"/>
+      <x:c r="N9"/>
+      <x:c r="O9"/>
+      <x:c r="P9"/>
+    </x:row>
+    <x:row r="10" ht="36" customHeight="1">
+      <x:c r="A10" s="358" t="str">
         <x:v>青色Button</x:v>
       </x:c>
-      <x:c r="B12" s="67" t="str">
-        <x:v>青色Button</x:v>
-      </x:c>
-      <x:c r="C12" s="67" t="str">
-        <x:v>青色Button</x:v>
-      </x:c>
-      <x:c r="D12" s="67" t="str">
-        <x:v>青色Button</x:v>
-      </x:c>
-      <x:c r="E12" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-      <x:c r="F12" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-      <x:c r="G12" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-      <x:c r="H12" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-      <x:c r="I12" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-      <x:c r="J12" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-      <x:c r="K12" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-      <x:c r="L12" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-      <x:c r="M12" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-      <x:c r="N12" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-      <x:c r="O12" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-      <x:c r="P12" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="22" customHeight="1">
-      <x:c r="A13" s="67" t="str">
-        <x:v>青色Button</x:v>
-      </x:c>
-      <x:c r="B13" s="67" t="str">
-        <x:v>青色Button</x:v>
-      </x:c>
-      <x:c r="C13" s="67" t="str">
-        <x:v>青色Button</x:v>
-      </x:c>
-      <x:c r="D13" s="67" t="str">
-        <x:v>青色Button</x:v>
-      </x:c>
-      <x:c r="E13" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-      <x:c r="F13" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-      <x:c r="G13" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-      <x:c r="H13" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-      <x:c r="I13" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-      <x:c r="J13" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-      <x:c r="K13" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-      <x:c r="L13" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-      <x:c r="M13" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-      <x:c r="N13" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-      <x:c r="O13" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-      <x:c r="P13" s="63" t="str">
-        <x:v>主要操作（検索、保存、新規等）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="59" t="str">
+      <x:c r="B10" s="358" t="str">
+        <x:v>主要操作（検索、保存、新規）</x:v>
+      </x:c>
+      <x:c r="C10"/>
+      <x:c r="D10"/>
+      <x:c r="E10"/>
+      <x:c r="F10"/>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
+      <x:c r="M10"/>
+      <x:c r="N10"/>
+      <x:c r="O10"/>
+      <x:c r="P10"/>
+    </x:row>
+    <x:row r="11" ht="36" customHeight="1">
+      <x:c r="A11" s="357" t="str">
         <x:v>灰色Button</x:v>
       </x:c>
-      <x:c r="B14" s="59" t="str">
-        <x:v>灰色Button</x:v>
-      </x:c>
-      <x:c r="C14" s="59" t="str">
-        <x:v>灰色Button</x:v>
-      </x:c>
-      <x:c r="D14" s="59" t="str">
-        <x:v>灰色Button</x:v>
-      </x:c>
-      <x:c r="E14" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
-      <x:c r="F14" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
-      <x:c r="G14" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
-      <x:c r="H14" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
-      <x:c r="I14" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
-      <x:c r="J14" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
-      <x:c r="K14" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
-      <x:c r="L14" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
-      <x:c r="M14" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
-      <x:c r="N14" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
-      <x:c r="O14" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
-      <x:c r="P14" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
+      <x:c r="B11" s="357" t="str">
+        <x:v>補助操作（クリア、取消、戻る）</x:v>
+      </x:c>
+      <x:c r="C11"/>
+      <x:c r="D11"/>
+      <x:c r="E11"/>
+      <x:c r="F11"/>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
+      <x:c r="M11"/>
+      <x:c r="N11"/>
+      <x:c r="O11"/>
+      <x:c r="P11"/>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="358" t="str">
+        <x:v>共通Header</x:v>
+      </x:c>
+      <x:c r="B12" s="358" t="str">
+        <x:v>System名、通知、User名、Logout。動作は14_共通レイアウト・19_共通API呼出。</x:v>
+      </x:c>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
+      <x:c r="E12"/>
+      <x:c r="F12"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
+      <x:c r="M12"/>
+      <x:c r="N12"/>
+      <x:c r="O12"/>
+      <x:c r="P12"/>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="357" t="str">
+        <x:v>Side Menu</x:v>
+      </x:c>
+      <x:c r="B13" s="357" t="str">
+        <x:v>Home、組織管理、Project、Task、日報、通知、System。表示条件は02のMenu権限。</x:v>
+      </x:c>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
+      <x:c r="M13"/>
+      <x:c r="N13"/>
+      <x:c r="O13"/>
+      <x:c r="P13"/>
+    </x:row>
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="358" t="str">
+        <x:v>Breadcrumb / Main Content</x:v>
+      </x:c>
+      <x:c r="B14" s="358" t="str">
+        <x:v>検索条件、一覧、入力Form、詳細、Kanban。固有配置は04～09のWF_SCR Sheet。</x:v>
+      </x:c>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
+      <x:c r="M14"/>
+      <x:c r="N14"/>
+      <x:c r="O14"/>
+      <x:c r="P14"/>
     </x:row>
     <x:row r="15" ht="22" customHeight="1">
-      <x:c r="A15" s="59" t="str">
-        <x:v>灰色Button</x:v>
-      </x:c>
-      <x:c r="B15" s="59" t="str">
-        <x:v>灰色Button</x:v>
-      </x:c>
-      <x:c r="C15" s="59" t="str">
-        <x:v>灰色Button</x:v>
-      </x:c>
-      <x:c r="D15" s="59" t="str">
-        <x:v>灰色Button</x:v>
-      </x:c>
-      <x:c r="E15" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
-      <x:c r="F15" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
-      <x:c r="G15" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
-      <x:c r="H15" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
-      <x:c r="I15" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
-      <x:c r="J15" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
-      <x:c r="K15" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
-      <x:c r="L15" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
-      <x:c r="M15" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
-      <x:c r="N15" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
-      <x:c r="O15" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
-      <x:c r="P15" s="63" t="str">
-        <x:v>補助操作（クリア、取消、戻る等）</x:v>
-      </x:c>
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
+      <x:c r="M15"/>
+      <x:c r="N15"/>
+      <x:c r="O15"/>
+      <x:c r="P15"/>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
-      <x:c r="A16" s="48"/>
-      <x:c r="B16" s="48"/>
-      <x:c r="C16" s="48"/>
-      <x:c r="D16" s="48"/>
-      <x:c r="E16" s="48"/>
-      <x:c r="F16" s="48"/>
-      <x:c r="G16" s="48"/>
-      <x:c r="H16" s="48"/>
-      <x:c r="I16" s="48"/>
-      <x:c r="J16" s="48"/>
-      <x:c r="K16" s="48"/>
-      <x:c r="L16" s="48"/>
-      <x:c r="M16" s="48"/>
-      <x:c r="N16" s="48"/>
-      <x:c r="O16" s="48"/>
-      <x:c r="P16" s="48"/>
+      <x:c r="A16"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
+      <x:c r="M16"/>
+      <x:c r="N16"/>
+      <x:c r="O16"/>
+      <x:c r="P16"/>
     </x:row>
     <x:row r="17" ht="22" customHeight="1">
-      <x:c r="A17" s="48"/>
-      <x:c r="B17" s="48"/>
-      <x:c r="C17" s="48"/>
-      <x:c r="D17" s="48"/>
-      <x:c r="E17" s="48"/>
-      <x:c r="F17" s="48"/>
-      <x:c r="G17" s="48"/>
-      <x:c r="H17" s="48"/>
-      <x:c r="I17" s="48"/>
-      <x:c r="J17" s="48"/>
-      <x:c r="K17" s="48"/>
-      <x:c r="L17" s="48"/>
-      <x:c r="M17" s="48"/>
-      <x:c r="N17" s="48"/>
-      <x:c r="O17" s="48"/>
-      <x:c r="P17" s="48"/>
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
+      <x:c r="I17"/>
+      <x:c r="J17"/>
+      <x:c r="K17"/>
+      <x:c r="L17"/>
+      <x:c r="M17"/>
+      <x:c r="N17"/>
+      <x:c r="O17"/>
+      <x:c r="P17"/>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
-      <x:c r="A18" s="54" t="str">
-        <x:v>2. 共通画面構成</x:v>
-      </x:c>
-      <x:c r="B18" s="54" t="str">
-        <x:v>2. 共通画面構成</x:v>
-      </x:c>
-      <x:c r="C18" s="54" t="str">
-        <x:v>2. 共通画面構成</x:v>
-      </x:c>
-      <x:c r="D18" s="54" t="str">
-        <x:v>2. 共通画面構成</x:v>
-      </x:c>
-      <x:c r="E18" s="54" t="str">
-        <x:v>2. 共通画面構成</x:v>
-      </x:c>
-      <x:c r="F18" s="54" t="str">
-        <x:v>2. 共通画面構成</x:v>
-      </x:c>
-      <x:c r="G18" s="54" t="str">
-        <x:v>2. 共通画面構成</x:v>
-      </x:c>
-      <x:c r="H18" s="54" t="str">
-        <x:v>2. 共通画面構成</x:v>
-      </x:c>
-      <x:c r="I18" s="54" t="str">
-        <x:v>2. 共通画面構成</x:v>
-      </x:c>
-      <x:c r="J18" s="54" t="str">
-        <x:v>2. 共通画面構成</x:v>
-      </x:c>
-      <x:c r="K18" s="54" t="str">
-        <x:v>2. 共通画面構成</x:v>
-      </x:c>
-      <x:c r="L18" s="54" t="str">
-        <x:v>2. 共通画面構成</x:v>
-      </x:c>
-      <x:c r="M18" s="54" t="str">
-        <x:v>2. 共通画面構成</x:v>
-      </x:c>
-      <x:c r="N18" s="54" t="str">
-        <x:v>2. 共通画面構成</x:v>
-      </x:c>
-      <x:c r="O18" s="54" t="str">
-        <x:v>2. 共通画面構成</x:v>
-      </x:c>
-      <x:c r="P18" s="54" t="str">
-        <x:v>2. 共通画面構成</x:v>
-      </x:c>
+      <x:c r="A18"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+      <x:c r="G18"/>
+      <x:c r="H18"/>
+      <x:c r="I18"/>
+      <x:c r="J18"/>
+      <x:c r="K18"/>
+      <x:c r="L18"/>
+      <x:c r="M18"/>
+      <x:c r="N18"/>
+      <x:c r="O18"/>
+      <x:c r="P18"/>
     </x:row>
     <x:row r="19" ht="22" customHeight="1">
-      <x:c r="A19" s="48"/>
-      <x:c r="B19" s="48"/>
-      <x:c r="C19" s="48"/>
-      <x:c r="D19" s="48"/>
-      <x:c r="E19" s="48"/>
-      <x:c r="F19" s="48"/>
-      <x:c r="G19" s="48"/>
-      <x:c r="H19" s="48"/>
-      <x:c r="I19" s="48"/>
-      <x:c r="J19" s="48"/>
-      <x:c r="K19" s="48"/>
-      <x:c r="L19" s="48"/>
-      <x:c r="M19" s="48"/>
-      <x:c r="N19" s="48"/>
-      <x:c r="O19" s="48"/>
-      <x:c r="P19" s="48"/>
+      <x:c r="A19"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
+      <x:c r="I19"/>
+      <x:c r="J19"/>
+      <x:c r="K19"/>
+      <x:c r="L19"/>
+      <x:c r="M19"/>
+      <x:c r="N19"/>
+      <x:c r="O19"/>
+      <x:c r="P19"/>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="B20" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="C20" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="D20" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="E20" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="F20" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="G20" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="H20" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="I20" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="J20" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="K20" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="L20" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="M20" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="N20" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="O20" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="P20" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
+      <x:c r="A20"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
+      <x:c r="I20"/>
+      <x:c r="J20"/>
+      <x:c r="K20"/>
+      <x:c r="L20"/>
+      <x:c r="M20"/>
+      <x:c r="N20"/>
+      <x:c r="O20"/>
+      <x:c r="P20"/>
     </x:row>
     <x:row r="21" ht="22" customHeight="1">
-      <x:c r="A21" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="B21" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="C21" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="D21" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="E21" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="F21" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="G21" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="H21" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="I21" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="J21" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="K21" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="L21" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="M21" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="N21" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="O21" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="P21" s="69" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
+      <x:c r="A21"/>
+      <x:c r="B21"/>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
+      <x:c r="G21"/>
+      <x:c r="H21"/>
+      <x:c r="I21"/>
+      <x:c r="J21"/>
+      <x:c r="K21"/>
+      <x:c r="L21"/>
+      <x:c r="M21"/>
+      <x:c r="N21"/>
+      <x:c r="O21"/>
+      <x:c r="P21"/>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="90" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B22" s="91" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C22" s="92" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D22" s="55" t="str">
-        <x:v>Breadcrumb</x:v>
-      </x:c>
-      <x:c r="E22" s="55" t="str">
-        <x:v>Breadcrumb</x:v>
-      </x:c>
-      <x:c r="F22" s="55" t="str">
-        <x:v>Breadcrumb</x:v>
-      </x:c>
-      <x:c r="G22" s="55" t="str">
-        <x:v>Breadcrumb</x:v>
-      </x:c>
-      <x:c r="H22" s="55" t="str">
-        <x:v>Breadcrumb</x:v>
-      </x:c>
-      <x:c r="I22" s="55" t="str">
-        <x:v>Breadcrumb</x:v>
-      </x:c>
-      <x:c r="J22" s="55" t="str">
-        <x:v>Breadcrumb</x:v>
-      </x:c>
-      <x:c r="K22" s="55" t="str">
-        <x:v>Breadcrumb</x:v>
-      </x:c>
-      <x:c r="L22" s="55" t="str">
-        <x:v>Breadcrumb</x:v>
-      </x:c>
-      <x:c r="M22" s="55" t="str">
-        <x:v>Breadcrumb</x:v>
-      </x:c>
-      <x:c r="N22" s="55" t="str">
-        <x:v>Breadcrumb</x:v>
-      </x:c>
-      <x:c r="O22" s="55" t="str">
-        <x:v>Breadcrumb</x:v>
-      </x:c>
-      <x:c r="P22" s="55" t="str">
-        <x:v>Breadcrumb</x:v>
-      </x:c>
+      <x:c r="A22"/>
+      <x:c r="B22"/>
+      <x:c r="C22"/>
+      <x:c r="D22"/>
+      <x:c r="E22"/>
+      <x:c r="F22"/>
+      <x:c r="G22"/>
+      <x:c r="H22"/>
+      <x:c r="I22"/>
+      <x:c r="J22"/>
+      <x:c r="K22"/>
+      <x:c r="L22"/>
+      <x:c r="M22"/>
+      <x:c r="N22"/>
+      <x:c r="O22"/>
+      <x:c r="P22"/>
     </x:row>
     <x:row r="23" ht="22" customHeight="1">
-      <x:c r="A23" s="93" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B23" s="94" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C23" s="95" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D23" s="127" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="E23" s="128" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="F23" s="128" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="G23" s="128" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="H23" s="128" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="I23" s="128" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="J23" s="128" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="K23" s="128" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="L23" s="128" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="M23" s="128" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="N23" s="128" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="O23" s="128" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="P23" s="129" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
+      <x:c r="A23"/>
+      <x:c r="B23"/>
+      <x:c r="C23"/>
+      <x:c r="D23"/>
+      <x:c r="E23"/>
+      <x:c r="F23"/>
+      <x:c r="G23"/>
+      <x:c r="H23"/>
+      <x:c r="I23"/>
+      <x:c r="J23"/>
+      <x:c r="K23"/>
+      <x:c r="L23"/>
+      <x:c r="M23"/>
+      <x:c r="N23"/>
+      <x:c r="O23"/>
+      <x:c r="P23"/>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="93" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B24" s="94" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C24" s="95" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D24" s="130" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="E24" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="F24" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="G24" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="H24" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="I24" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="J24" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="K24" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="L24" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="M24" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="N24" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="O24" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="P24" s="132" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
+      <x:c r="A24"/>
+      <x:c r="B24"/>
+      <x:c r="C24"/>
+      <x:c r="D24"/>
+      <x:c r="E24"/>
+      <x:c r="F24"/>
+      <x:c r="G24"/>
+      <x:c r="H24"/>
+      <x:c r="I24"/>
+      <x:c r="J24"/>
+      <x:c r="K24"/>
+      <x:c r="L24"/>
+      <x:c r="M24"/>
+      <x:c r="N24"/>
+      <x:c r="O24"/>
+      <x:c r="P24"/>
     </x:row>
     <x:row r="25" ht="22" customHeight="1">
-      <x:c r="A25" s="93" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B25" s="94" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C25" s="95" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D25" s="130" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="E25" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="F25" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="G25" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="H25" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="I25" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="J25" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="K25" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="L25" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="M25" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="N25" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="O25" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="P25" s="132" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
+      <x:c r="A25"/>
+      <x:c r="B25"/>
+      <x:c r="C25"/>
+      <x:c r="D25"/>
+      <x:c r="E25"/>
+      <x:c r="F25"/>
+      <x:c r="G25"/>
+      <x:c r="H25"/>
+      <x:c r="I25"/>
+      <x:c r="J25"/>
+      <x:c r="K25"/>
+      <x:c r="L25"/>
+      <x:c r="M25"/>
+      <x:c r="N25"/>
+      <x:c r="O25"/>
+      <x:c r="P25"/>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
-      <x:c r="A26" s="93" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B26" s="94" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C26" s="95" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D26" s="130" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="E26" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="F26" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="G26" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="H26" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="I26" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="J26" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="K26" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="L26" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="M26" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="N26" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="O26" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="P26" s="132" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
+      <x:c r="A26"/>
+      <x:c r="B26"/>
+      <x:c r="C26"/>
+      <x:c r="D26"/>
+      <x:c r="E26"/>
+      <x:c r="F26"/>
+      <x:c r="G26"/>
+      <x:c r="H26"/>
+      <x:c r="I26"/>
+      <x:c r="J26"/>
+      <x:c r="K26"/>
+      <x:c r="L26"/>
+      <x:c r="M26"/>
+      <x:c r="N26"/>
+      <x:c r="O26"/>
+      <x:c r="P26"/>
     </x:row>
     <x:row r="27" ht="22" customHeight="1">
-      <x:c r="A27" s="93" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B27" s="94" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C27" s="95" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D27" s="130" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="E27" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="F27" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="G27" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="H27" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="I27" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="J27" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="K27" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="L27" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="M27" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="N27" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="O27" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="P27" s="132" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
+      <x:c r="A27"/>
+      <x:c r="B27"/>
+      <x:c r="C27"/>
+      <x:c r="D27"/>
+      <x:c r="E27"/>
+      <x:c r="F27"/>
+      <x:c r="G27"/>
+      <x:c r="H27"/>
+      <x:c r="I27"/>
+      <x:c r="J27"/>
+      <x:c r="K27"/>
+      <x:c r="L27"/>
+      <x:c r="M27"/>
+      <x:c r="N27"/>
+      <x:c r="O27"/>
+      <x:c r="P27"/>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
-      <x:c r="A28" s="93" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B28" s="94" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C28" s="95" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D28" s="130" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="E28" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="F28" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="G28" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="H28" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="I28" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="J28" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="K28" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="L28" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="M28" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="N28" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="O28" s="131" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="P28" s="132" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
+      <x:c r="A28"/>
+      <x:c r="B28"/>
+      <x:c r="C28"/>
+      <x:c r="D28"/>
+      <x:c r="E28"/>
+      <x:c r="F28"/>
+      <x:c r="G28"/>
+      <x:c r="H28"/>
+      <x:c r="I28"/>
+      <x:c r="J28"/>
+      <x:c r="K28"/>
+      <x:c r="L28"/>
+      <x:c r="M28"/>
+      <x:c r="N28"/>
+      <x:c r="O28"/>
+      <x:c r="P28"/>
     </x:row>
     <x:row r="29" ht="22" customHeight="1">
-      <x:c r="A29" s="96" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B29" s="97" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C29" s="98" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D29" s="133" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="E29" s="134" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="F29" s="134" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="G29" s="134" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="H29" s="134" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="I29" s="134" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="J29" s="134" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="K29" s="134" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="L29" s="134" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="M29" s="134" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="N29" s="134" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="O29" s="134" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
-      <x:c r="P29" s="135" t="str">
-        <x:v>Main Content
-検索条件 / 一覧 / 入力Form / 詳細 / Kanban</x:v>
-      </x:c>
+      <x:c r="A29"/>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
+      <x:c r="G29"/>
+      <x:c r="H29"/>
+      <x:c r="I29"/>
+      <x:c r="J29"/>
+      <x:c r="K29"/>
+      <x:c r="L29"/>
+      <x:c r="M29"/>
+      <x:c r="N29"/>
+      <x:c r="O29"/>
+      <x:c r="P29"/>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="48"/>
-      <x:c r="B30" s="48"/>
-      <x:c r="C30" s="48"/>
-      <x:c r="D30" s="48"/>
-      <x:c r="E30" s="48"/>
-      <x:c r="F30" s="48"/>
-      <x:c r="G30" s="48"/>
-      <x:c r="H30" s="48"/>
-      <x:c r="I30" s="48"/>
-      <x:c r="J30" s="48"/>
-      <x:c r="K30" s="48"/>
-      <x:c r="L30" s="48"/>
-      <x:c r="M30" s="48"/>
-      <x:c r="N30" s="48"/>
-      <x:c r="O30" s="48"/>
-      <x:c r="P30" s="48"/>
+      <x:c r="A30"/>
+      <x:c r="B30"/>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
+      <x:c r="F30"/>
+      <x:c r="G30"/>
+      <x:c r="H30"/>
+      <x:c r="I30"/>
+      <x:c r="J30"/>
+      <x:c r="K30"/>
+      <x:c r="L30"/>
+      <x:c r="M30"/>
+      <x:c r="N30"/>
+      <x:c r="O30"/>
+      <x:c r="P30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:P2"/>
-    <x:mergeCell ref="A4:P4"/>
-    <x:mergeCell ref="A6:D7"/>
-    <x:mergeCell ref="E6:P7"/>
-    <x:mergeCell ref="A8:D9"/>
-    <x:mergeCell ref="E8:P9"/>
-    <x:mergeCell ref="A10:D11"/>
-    <x:mergeCell ref="E10:P11"/>
-    <x:mergeCell ref="A12:D13"/>
-    <x:mergeCell ref="E12:P13"/>
-    <x:mergeCell ref="A14:D15"/>
-    <x:mergeCell ref="E14:P15"/>
-    <x:mergeCell ref="A18:P18"/>
-    <x:mergeCell ref="A20:P21"/>
-    <x:mergeCell ref="A22:C29"/>
-    <x:mergeCell ref="D22:P22"/>
-    <x:mergeCell ref="D23:P29"/>
+    <x:mergeCell ref="A1:B1"/>
+    <x:mergeCell ref="A3:B3"/>
+    <x:mergeCell ref="A5:B5"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5850,6 +6780,11 @@
       <x:c r="E1" s="201"/>
       <x:c r="F1" s="201"/>
       <x:c r="G1" s="201"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="201"/>
@@ -5859,6 +6794,11 @@
       <x:c r="E2" s="201"/>
       <x:c r="F2" s="201"/>
       <x:c r="G2" s="201"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="204" t="str">
@@ -5868,31 +6808,55 @@
         <x:v>Company WorkHub</x:v>
       </x:c>
       <x:c r="C3" s="202"/>
-      <x:c r="D3" s="204" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="D3" s="350" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="E3" s="202" t="str">
         <x:v>CW-BD-SCR-019</x:v>
       </x:c>
       <x:c r="F3" s="202"/>
       <x:c r="G3" s="202"/>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="204" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="B4" s="202" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="B4" s="151" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="C4" s="202"/>
       <x:c r="D4" s="204" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="E4" s="202" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="E4" s="151" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="F4" s="202"/>
       <x:c r="G4" s="202"/>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5"/>
+      <x:c r="B5"/>
+      <x:c r="C5"/>
+      <x:c r="D5"/>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="205" t="str">
@@ -5904,6 +6868,11 @@
       <x:c r="E6" s="205"/>
       <x:c r="F6" s="205"/>
       <x:c r="G6" s="205"/>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="210" t="str">
@@ -5927,6 +6896,11 @@
       <x:c r="G7" s="210" t="str">
         <x:v>実装位置</x:v>
       </x:c>
+      <x:c r="H7"/>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="214" t="str">
@@ -5950,6 +6924,11 @@
       <x:c r="G8" s="214" t="str">
         <x:v>App初期化処理</x:v>
       </x:c>
+      <x:c r="H8"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="214" t="str">
@@ -5973,6 +6952,11 @@
       <x:c r="G9" s="214" t="str">
         <x:v>Axios共通Interceptor</x:v>
       </x:c>
+      <x:c r="H9"/>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="214" t="str">
@@ -5996,6 +6980,39 @@
       <x:c r="G10" s="214" t="str">
         <x:v>共通Header</x:v>
       </x:c>
+      <x:c r="H10"/>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>CMN-NTF-001</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>App初期化後／通知既読後</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>API-NTF-002</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>Authorization Bearer</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>未読件数をHeaderへ表示</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>失敗時は件数を非表示、画面本体は継続</x:v>
+      </x:c>
+      <x:c r="G11" t="str">
+        <x:v>共通Header Store</x:v>
+      </x:c>
+      <x:c r="H11"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="218" t="str">
@@ -6007,6 +7024,11 @@
       <x:c r="E12" s="218"/>
       <x:c r="F12" s="218"/>
       <x:c r="G12" s="218"/>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="218"/>
@@ -6016,6 +7038,53 @@
       <x:c r="E13" s="218"/>
       <x:c r="F13" s="218"/>
       <x:c r="G13" s="218"/>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -6025,4 +7094,1111 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="7" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="38" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="26" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="309" t="str">
+        <x:v>画面Route定義</x:v>
+      </x:c>
+      <x:c r="B1" s="309" t="str"/>
+      <x:c r="C1" s="309" t="str"/>
+      <x:c r="D1" s="309" t="str"/>
+      <x:c r="E1" s="309" t="str"/>
+      <x:c r="F1" s="309" t="str"/>
+      <x:c r="G1" s="309" t="str"/>
+      <x:c r="H1" s="309" t="str"/>
+      <x:c r="I1" s="309" t="str"/>
+      <x:c r="J1" s="309" t="str"/>
+      <x:c r="K1" s="309" t="str"/>
+      <x:c r="L1" s="309" t="str"/>
+    </x:row>
+    <x:row r="2" ht="27" customHeight="1">
+      <x:c r="A2" s="309" t="str"/>
+      <x:c r="B2" s="309" t="str"/>
+      <x:c r="C2" s="309" t="str"/>
+      <x:c r="D2" s="309" t="str"/>
+      <x:c r="E2" s="309" t="str"/>
+      <x:c r="F2" s="309" t="str"/>
+      <x:c r="G2" s="309" t="str"/>
+      <x:c r="H2" s="309" t="str"/>
+      <x:c r="I2" s="309" t="str"/>
+      <x:c r="J2" s="309" t="str"/>
+      <x:c r="K2" s="309" t="str"/>
+      <x:c r="L2" s="309" t="str"/>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="314" t="str">
+        <x:v>システム名</x:v>
+      </x:c>
+      <x:c r="B3" s="314" t="str"/>
+      <x:c r="C3" s="315" t="str">
+        <x:v>Company WorkHub</x:v>
+      </x:c>
+      <x:c r="D3" s="315" t="str"/>
+      <x:c r="E3" s="315" t="str"/>
+      <x:c r="F3" s="315" t="str"/>
+      <x:c r="G3" s="315" t="str"/>
+      <x:c r="H3" s="315" t="str"/>
+      <x:c r="I3" s="362" t="str">
+        <x:v>章ID</x:v>
+      </x:c>
+      <x:c r="J3" s="314" t="str"/>
+      <x:c r="K3" s="315" t="str">
+        <x:v>CW-BD-048</x:v>
+      </x:c>
+      <x:c r="L3" s="315" t="str"/>
+    </x:row>
+    <x:row r="4" ht="22" customHeight="1">
+      <x:c r="A4" s="314" t="str">
+        <x:v>版数</x:v>
+      </x:c>
+      <x:c r="B4" s="314" t="str"/>
+      <x:c r="C4" s="363" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="D4" s="315" t="str"/>
+      <x:c r="E4" s="315" t="str"/>
+      <x:c r="F4" s="315" t="str"/>
+      <x:c r="G4" s="315" t="str"/>
+      <x:c r="H4" s="315" t="str"/>
+      <x:c r="I4" s="362" t="str">
+        <x:v>作成日：2026-09-24</x:v>
+      </x:c>
+      <x:c r="J4" s="314"/>
+      <x:c r="K4" s="363" t="str">
+        <x:v>2026-09-24</x:v>
+      </x:c>
+      <x:c r="L4" s="315" t="str"/>
+    </x:row>
+    <x:row r="5" ht="22" customHeight="1">
+      <x:c r="A5" s="314" t="str">
+        <x:v>基本設計参照</x:v>
+      </x:c>
+      <x:c r="B5" s="314" t="str"/>
+      <x:c r="C5" s="315" t="str">
+        <x:v>12_画面一覧/13_画面遷移</x:v>
+      </x:c>
+      <x:c r="D5" s="315" t="str"/>
+      <x:c r="E5" s="315" t="str"/>
+      <x:c r="F5" s="315" t="str"/>
+      <x:c r="G5" s="315" t="str"/>
+      <x:c r="H5" s="315" t="str"/>
+      <x:c r="I5" s="314" t="str">
+        <x:v>作成者</x:v>
+      </x:c>
+      <x:c r="J5" s="314" t="str"/>
+      <x:c r="K5" s="315" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="L5" s="315" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6"/>
+      <x:c r="B6"/>
+      <x:c r="C6"/>
+      <x:c r="D6"/>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="319" t="str">
+        <x:v>1. React Route一覧</x:v>
+      </x:c>
+      <x:c r="B7" s="319" t="str"/>
+      <x:c r="C7" s="319" t="str"/>
+      <x:c r="D7" s="319" t="str"/>
+      <x:c r="E7" s="319" t="str"/>
+      <x:c r="F7" s="319" t="str"/>
+      <x:c r="G7" s="319" t="str"/>
+      <x:c r="H7" s="319" t="str"/>
+      <x:c r="I7" s="319" t="str"/>
+      <x:c r="J7" s="319" t="str"/>
+      <x:c r="K7" s="319" t="str"/>
+      <x:c r="L7" s="319" t="str"/>
+    </x:row>
+    <x:row r="8" ht="28" customHeight="1">
+      <x:c r="A8" s="324" t="str">
+        <x:v>No.</x:v>
+      </x:c>
+      <x:c r="B8" s="324" t="str">
+        <x:v>画面ID</x:v>
+      </x:c>
+      <x:c r="C8" s="324" t="str">
+        <x:v>画面名</x:v>
+      </x:c>
+      <x:c r="D8" s="324" t="str">
+        <x:v>Route Path</x:v>
+      </x:c>
+      <x:c r="E8" s="324" t="str">
+        <x:v>認証</x:v>
+      </x:c>
+      <x:c r="F8" s="324" t="str">
+        <x:v>利用Role</x:v>
+      </x:c>
+      <x:c r="G8" s="324" t="str">
+        <x:v>Path Parameter</x:v>
+      </x:c>
+      <x:c r="H8" s="324" t="str">
+        <x:v>直接URL</x:v>
+      </x:c>
+      <x:c r="I8" s="324" t="str">
+        <x:v>備考</x:v>
+      </x:c>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
+    </x:row>
+    <x:row r="9" ht="34" customHeight="1">
+      <x:c r="A9" s="328" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B9" s="328" t="str">
+        <x:v>SCR-001</x:v>
+      </x:c>
+      <x:c r="C9" s="328" t="str">
+        <x:v>ログイン</x:v>
+      </x:c>
+      <x:c r="D9" s="328" t="str">
+        <x:v>/login</x:v>
+      </x:c>
+      <x:c r="E9" s="328" t="str">
+        <x:v>不要</x:v>
+      </x:c>
+      <x:c r="F9" s="328" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="G9" s="328" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H9" s="328" t="str">
+        <x:v>可</x:v>
+      </x:c>
+      <x:c r="I9" s="345" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
+    </x:row>
+    <x:row r="10" ht="34" customHeight="1">
+      <x:c r="A10" s="329" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B10" s="329" t="str">
+        <x:v>SCR-002</x:v>
+      </x:c>
+      <x:c r="C10" s="329" t="str">
+        <x:v>ホームダッシュボード</x:v>
+      </x:c>
+      <x:c r="D10" s="329" t="str">
+        <x:v>/home</x:v>
+      </x:c>
+      <x:c r="E10" s="329" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F10" s="329" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="G10" s="329" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H10" s="329" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I10" s="329" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
+    </x:row>
+    <x:row r="11" ht="34" customHeight="1">
+      <x:c r="A11" s="328" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B11" s="328" t="str">
+        <x:v>SCR-026</x:v>
+      </x:c>
+      <x:c r="C11" s="328" t="str">
+        <x:v>パスワード変更</x:v>
+      </x:c>
+      <x:c r="D11" s="328" t="str">
+        <x:v>/settings/password</x:v>
+      </x:c>
+      <x:c r="E11" s="328" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F11" s="328" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="G11" s="328" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H11" s="328" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I11" s="345" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
+    </x:row>
+    <x:row r="12" ht="34" customHeight="1">
+      <x:c r="A12" s="329" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B12" s="329" t="str">
+        <x:v>SCR-003</x:v>
+      </x:c>
+      <x:c r="C12" s="329" t="str">
+        <x:v>従業員一覧</x:v>
+      </x:c>
+      <x:c r="D12" s="329" t="str">
+        <x:v>/employees</x:v>
+      </x:c>
+      <x:c r="E12" s="329" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F12" s="329" t="str">
+        <x:v>管理者/PM</x:v>
+      </x:c>
+      <x:c r="G12" s="329" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H12" s="329" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I12" s="329" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
+    </x:row>
+    <x:row r="13" ht="34" customHeight="1">
+      <x:c r="A13" s="328" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B13" s="328" t="str">
+        <x:v>SCR-004</x:v>
+      </x:c>
+      <x:c r="C13" s="328" t="str">
+        <x:v>従業員登録</x:v>
+      </x:c>
+      <x:c r="D13" s="328" t="str">
+        <x:v>/employees/new</x:v>
+      </x:c>
+      <x:c r="E13" s="328" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F13" s="328" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="G13" s="328" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H13" s="328" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I13" s="345" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
+    </x:row>
+    <x:row r="14" ht="34" customHeight="1">
+      <x:c r="A14" s="329" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B14" s="329" t="str">
+        <x:v>SCR-005</x:v>
+      </x:c>
+      <x:c r="C14" s="329" t="str">
+        <x:v>従業員編集</x:v>
+      </x:c>
+      <x:c r="D14" s="329" t="str">
+        <x:v>/employees/:employeeId/edit</x:v>
+      </x:c>
+      <x:c r="E14" s="329" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F14" s="329" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="G14" s="329" t="str">
+        <x:v>:employeeId</x:v>
+      </x:c>
+      <x:c r="H14" s="329" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I14" s="329" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
+    </x:row>
+    <x:row r="15" ht="34" customHeight="1">
+      <x:c r="A15" s="328" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B15" s="328" t="str">
+        <x:v>SCR-006</x:v>
+      </x:c>
+      <x:c r="C15" s="328" t="str">
+        <x:v>従業員詳細</x:v>
+      </x:c>
+      <x:c r="D15" s="328" t="str">
+        <x:v>/employees/:employeeId</x:v>
+      </x:c>
+      <x:c r="E15" s="328" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F15" s="328" t="str">
+        <x:v>管理者/PM</x:v>
+      </x:c>
+      <x:c r="G15" s="328" t="str">
+        <x:v>:employeeId</x:v>
+      </x:c>
+      <x:c r="H15" s="328" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I15" s="345" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
+    </x:row>
+    <x:row r="16" ht="34" customHeight="1">
+      <x:c r="A16" s="329" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B16" s="329" t="str">
+        <x:v>SCR-007</x:v>
+      </x:c>
+      <x:c r="C16" s="329" t="str">
+        <x:v>部門管理</x:v>
+      </x:c>
+      <x:c r="D16" s="329" t="str">
+        <x:v>/departments</x:v>
+      </x:c>
+      <x:c r="E16" s="329" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F16" s="329" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="G16" s="329" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H16" s="329" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I16" s="329" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
+    </x:row>
+    <x:row r="17" ht="34" customHeight="1">
+      <x:c r="A17" s="328" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B17" s="328" t="str">
+        <x:v>SCR-008</x:v>
+      </x:c>
+      <x:c r="C17" s="328" t="str">
+        <x:v>プロジェクト一覧</x:v>
+      </x:c>
+      <x:c r="D17" s="328" t="str">
+        <x:v>/projects</x:v>
+      </x:c>
+      <x:c r="E17" s="328" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F17" s="328" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="G17" s="328" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H17" s="328" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I17" s="345" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="34" customHeight="1">
+      <x:c r="A18" s="329" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B18" s="329" t="str">
+        <x:v>SCR-009</x:v>
+      </x:c>
+      <x:c r="C18" s="329" t="str">
+        <x:v>プロジェクト登録</x:v>
+      </x:c>
+      <x:c r="D18" s="329" t="str">
+        <x:v>/projects/new</x:v>
+      </x:c>
+      <x:c r="E18" s="329" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F18" s="329" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="G18" s="329" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H18" s="329" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I18" s="329" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="34" customHeight="1">
+      <x:c r="A19" s="328" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B19" s="328" t="str">
+        <x:v>SCR-010</x:v>
+      </x:c>
+      <x:c r="C19" s="328" t="str">
+        <x:v>プロジェクト編集</x:v>
+      </x:c>
+      <x:c r="D19" s="328" t="str">
+        <x:v>/projects/:projectId/edit</x:v>
+      </x:c>
+      <x:c r="E19" s="328" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F19" s="328" t="str">
+        <x:v>管理者/PM</x:v>
+      </x:c>
+      <x:c r="G19" s="328" t="str">
+        <x:v>:projectId</x:v>
+      </x:c>
+      <x:c r="H19" s="328" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I19" s="345" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="34" customHeight="1">
+      <x:c r="A20" s="329" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B20" s="329" t="str">
+        <x:v>SCR-011</x:v>
+      </x:c>
+      <x:c r="C20" s="329" t="str">
+        <x:v>プロジェクト詳細</x:v>
+      </x:c>
+      <x:c r="D20" s="329" t="str">
+        <x:v>/projects/:projectId</x:v>
+      </x:c>
+      <x:c r="E20" s="329" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F20" s="329" t="str">
+        <x:v>関係者</x:v>
+      </x:c>
+      <x:c r="G20" s="329" t="str">
+        <x:v>:projectId</x:v>
+      </x:c>
+      <x:c r="H20" s="329" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I20" s="329" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="34" customHeight="1">
+      <x:c r="A21" s="328" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B21" s="328" t="str">
+        <x:v>SCR-012</x:v>
+      </x:c>
+      <x:c r="C21" s="328" t="str">
+        <x:v>プロジェクトメンバー管理</x:v>
+      </x:c>
+      <x:c r="D21" s="328" t="str">
+        <x:v>/projects/:projectId/members</x:v>
+      </x:c>
+      <x:c r="E21" s="328" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F21" s="328" t="str">
+        <x:v>管理者/PM</x:v>
+      </x:c>
+      <x:c r="G21" s="328" t="str">
+        <x:v>:projectId</x:v>
+      </x:c>
+      <x:c r="H21" s="328" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I21" s="345" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="34" customHeight="1">
+      <x:c r="A22" s="329" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B22" s="329" t="str">
+        <x:v>SCR-013</x:v>
+      </x:c>
+      <x:c r="C22" s="329" t="str">
+        <x:v>タスク一覧</x:v>
+      </x:c>
+      <x:c r="D22" s="329" t="str">
+        <x:v>/tasks</x:v>
+      </x:c>
+      <x:c r="E22" s="329" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F22" s="329" t="str">
+        <x:v>管理者/PM</x:v>
+      </x:c>
+      <x:c r="G22" s="329" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H22" s="329" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I22" s="329" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="34" customHeight="1">
+      <x:c r="A23" s="328" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B23" s="328" t="str">
+        <x:v>SCR-014</x:v>
+      </x:c>
+      <x:c r="C23" s="328" t="str">
+        <x:v>マイタスク</x:v>
+      </x:c>
+      <x:c r="D23" s="328" t="str">
+        <x:v>/my-tasks</x:v>
+      </x:c>
+      <x:c r="E23" s="328" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F23" s="328" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="G23" s="328" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H23" s="328" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I23" s="345" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="34" customHeight="1">
+      <x:c r="A24" s="329" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B24" s="329" t="str">
+        <x:v>SCR-015</x:v>
+      </x:c>
+      <x:c r="C24" s="329" t="str">
+        <x:v>タスク登録</x:v>
+      </x:c>
+      <x:c r="D24" s="329" t="str">
+        <x:v>/tasks/new</x:v>
+      </x:c>
+      <x:c r="E24" s="329" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F24" s="329" t="str">
+        <x:v>管理者/PM</x:v>
+      </x:c>
+      <x:c r="G24" s="329" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H24" s="329" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I24" s="329" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="34" customHeight="1">
+      <x:c r="A25" s="328" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B25" s="328" t="str">
+        <x:v>SCR-016</x:v>
+      </x:c>
+      <x:c r="C25" s="328" t="str">
+        <x:v>タスク編集</x:v>
+      </x:c>
+      <x:c r="D25" s="328" t="str">
+        <x:v>/tasks/:taskId/edit</x:v>
+      </x:c>
+      <x:c r="E25" s="328" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F25" s="328" t="str">
+        <x:v>管理者/PM</x:v>
+      </x:c>
+      <x:c r="G25" s="328" t="str">
+        <x:v>:taskId</x:v>
+      </x:c>
+      <x:c r="H25" s="328" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I25" s="345" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="34" customHeight="1">
+      <x:c r="A26" s="329" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B26" s="329" t="str">
+        <x:v>SCR-017</x:v>
+      </x:c>
+      <x:c r="C26" s="329" t="str">
+        <x:v>タスク詳細</x:v>
+      </x:c>
+      <x:c r="D26" s="329" t="str">
+        <x:v>/tasks/:taskId</x:v>
+      </x:c>
+      <x:c r="E26" s="329" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F26" s="329" t="str">
+        <x:v>関係者</x:v>
+      </x:c>
+      <x:c r="G26" s="329" t="str">
+        <x:v>:taskId</x:v>
+      </x:c>
+      <x:c r="H26" s="329" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I26" s="329" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="34" customHeight="1">
+      <x:c r="A27" s="328" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B27" s="328" t="str">
+        <x:v>SCR-018</x:v>
+      </x:c>
+      <x:c r="C27" s="328" t="str">
+        <x:v>タスクボード</x:v>
+      </x:c>
+      <x:c r="D27" s="328" t="str">
+        <x:v>/task-board</x:v>
+      </x:c>
+      <x:c r="E27" s="328" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F27" s="328" t="str">
+        <x:v>関係者</x:v>
+      </x:c>
+      <x:c r="G27" s="328" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H27" s="328" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I27" s="345" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="34" customHeight="1">
+      <x:c r="A28" s="329" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B28" s="329" t="str">
+        <x:v>SCR-019</x:v>
+      </x:c>
+      <x:c r="C28" s="329" t="str">
+        <x:v>マイ日報</x:v>
+      </x:c>
+      <x:c r="D28" s="329" t="str">
+        <x:v>/daily-reports/mine</x:v>
+      </x:c>
+      <x:c r="E28" s="329" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F28" s="329" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="G28" s="329" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H28" s="329" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I28" s="329" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="39" customHeight="1">
+      <x:c r="A29" s="328" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B29" s="328" t="str">
+        <x:v>SCR-020</x:v>
+      </x:c>
+      <x:c r="C29" s="328" t="str">
+        <x:v>日報登録</x:v>
+      </x:c>
+      <x:c r="D29" s="345" t="str">
+        <x:v>新規：/daily-reports/new ／編集：/daily-reports/:reportId/edit</x:v>
+      </x:c>
+      <x:c r="E29" s="328" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F29" s="328" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="G29" s="328" t="str">
+        <x:v>新規：reportId不要／編集：reportId必須</x:v>
+      </x:c>
+      <x:c r="H29" s="328" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I29" s="345" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="34" customHeight="1">
+      <x:c r="A30" s="329" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B30" s="329" t="str">
+        <x:v>SCR-021</x:v>
+      </x:c>
+      <x:c r="C30" s="329" t="str">
+        <x:v>日報検索</x:v>
+      </x:c>
+      <x:c r="D30" s="329" t="str">
+        <x:v>/daily-reports/search</x:v>
+      </x:c>
+      <x:c r="E30" s="329" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F30" s="329" t="str">
+        <x:v>管理者/PM</x:v>
+      </x:c>
+      <x:c r="G30" s="329" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H30" s="329" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I30" s="329" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="34" customHeight="1">
+      <x:c r="A31" s="328" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B31" s="328" t="str">
+        <x:v>SCR-022</x:v>
+      </x:c>
+      <x:c r="C31" s="328" t="str">
+        <x:v>通知一覧</x:v>
+      </x:c>
+      <x:c r="D31" s="328" t="str">
+        <x:v>/notifications</x:v>
+      </x:c>
+      <x:c r="E31" s="328" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F31" s="328" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="G31" s="328" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H31" s="328" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I31" s="345" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="34" customHeight="1">
+      <x:c r="A32" s="329" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B32" s="329" t="str">
+        <x:v>SCR-023</x:v>
+      </x:c>
+      <x:c r="C32" s="329" t="str">
+        <x:v>ユーザー管理</x:v>
+      </x:c>
+      <x:c r="D32" s="329" t="str">
+        <x:v>/admin/users</x:v>
+      </x:c>
+      <x:c r="E32" s="329" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F32" s="329" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="G32" s="329" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H32" s="329" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I32" s="329" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="34" customHeight="1">
+      <x:c r="A33" s="328" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B33" s="328" t="str">
+        <x:v>SCR-024</x:v>
+      </x:c>
+      <x:c r="C33" s="328" t="str">
+        <x:v>ロール管理</x:v>
+      </x:c>
+      <x:c r="D33" s="328" t="str">
+        <x:v>/admin/roles</x:v>
+      </x:c>
+      <x:c r="E33" s="328" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F33" s="328" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="G33" s="328" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H33" s="328" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I33" s="345" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="34" customHeight="1">
+      <x:c r="A34" s="329" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B34" s="329" t="str">
+        <x:v>SCR-025</x:v>
+      </x:c>
+      <x:c r="C34" s="329" t="str">
+        <x:v>操作ログ</x:v>
+      </x:c>
+      <x:c r="D34" s="329" t="str">
+        <x:v>/admin/operation-logs</x:v>
+      </x:c>
+      <x:c r="E34" s="329" t="str">
+        <x:v>必須</x:v>
+      </x:c>
+      <x:c r="F34" s="329" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="G34" s="329" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H34" s="329" t="str">
+        <x:v>認証/権限後可</x:v>
+      </x:c>
+      <x:c r="I34" s="329" t="str">
+        <x:v>Route正本。本Pathを詳細設計・実装で使用。権限は02参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="319" t="str">
+        <x:v>2. Route共通規則</x:v>
+      </x:c>
+      <x:c r="B37" s="319" t="str"/>
+      <x:c r="C37" s="319" t="str"/>
+      <x:c r="D37" s="319" t="str"/>
+      <x:c r="E37" s="319" t="str"/>
+      <x:c r="F37" s="319" t="str"/>
+      <x:c r="G37" s="319" t="str"/>
+      <x:c r="H37" s="319" t="str"/>
+      <x:c r="I37" s="319" t="str"/>
+      <x:c r="J37" s="319" t="str"/>
+      <x:c r="K37" s="319" t="str"/>
+      <x:c r="L37" s="319" t="str"/>
+    </x:row>
+    <x:row r="38" ht="221" customHeight="1">
+      <x:c r="A38" s="334" t="str">
+        <x:v>SCR-001のみ公開Route。保護Routeは認証と02のPermission/Data Scopeを確認。passwordMustChange=trueならSCR-026以外の業務Route・redirectは禁止しSCR-026へ。変更成功時はSessionを失効しSCR-001へ。通常redirectは登録済Routeかつ利用権限内のみ採用、それ以外はSCR-002。競合は入力保持、利用者が再取得を選んだ場合のみ最新値へ置換。不存在/不正Path/権限不足/システム異常は下記共通例外遷移に従う。</x:v>
+      </x:c>
+      <x:c r="B38" s="334" t="str"/>
+      <x:c r="C38" s="334" t="str"/>
+      <x:c r="D38" s="334" t="str"/>
+      <x:c r="E38" s="334" t="str"/>
+      <x:c r="F38" s="334" t="str"/>
+      <x:c r="G38" s="334" t="str"/>
+      <x:c r="H38" s="334" t="str"/>
+      <x:c r="I38" s="334" t="str"/>
+      <x:c r="J38" s="334" t="str"/>
+      <x:c r="K38" s="334" t="str"/>
+      <x:c r="L38" s="334" t="str"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="334" t="str"/>
+      <x:c r="B39" s="334" t="str"/>
+      <x:c r="C39" s="334" t="str"/>
+      <x:c r="D39" s="334" t="str"/>
+      <x:c r="E39" s="334" t="str"/>
+      <x:c r="F39" s="334" t="str"/>
+      <x:c r="G39" s="334" t="str"/>
+      <x:c r="H39" s="334" t="str"/>
+      <x:c r="I39" s="334" t="str"/>
+      <x:c r="J39" s="334" t="str"/>
+      <x:c r="K39" s="334" t="str"/>
+      <x:c r="L39" s="334" t="str"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="334" t="str"/>
+      <x:c r="B40" s="334" t="str"/>
+      <x:c r="C40" s="334" t="str"/>
+      <x:c r="D40" s="334" t="str"/>
+      <x:c r="E40" s="334" t="str"/>
+      <x:c r="F40" s="334" t="str"/>
+      <x:c r="G40" s="334" t="str"/>
+      <x:c r="H40" s="334" t="str"/>
+      <x:c r="I40" s="334" t="str"/>
+      <x:c r="J40" s="334" t="str"/>
+      <x:c r="K40" s="334" t="str"/>
+      <x:c r="L40" s="334" t="str"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="334" t="str"/>
+      <x:c r="B41" s="334" t="str"/>
+      <x:c r="C41" s="334" t="str"/>
+      <x:c r="D41" s="334" t="str"/>
+      <x:c r="E41" s="334" t="str"/>
+      <x:c r="F41" s="334" t="str"/>
+      <x:c r="G41" s="334" t="str"/>
+      <x:c r="H41" s="334" t="str"/>
+      <x:c r="I41" s="334" t="str"/>
+      <x:c r="J41" s="334" t="str"/>
+      <x:c r="K41" s="334" t="str"/>
+      <x:c r="L41" s="334" t="str"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="334" t="str"/>
+      <x:c r="B42" s="334" t="str"/>
+      <x:c r="C42" s="334" t="str"/>
+      <x:c r="D42" s="334" t="str"/>
+      <x:c r="E42" s="334" t="str"/>
+      <x:c r="F42" s="334" t="str"/>
+      <x:c r="G42" s="334" t="str"/>
+      <x:c r="H42" s="334" t="str"/>
+      <x:c r="I42" s="334" t="str"/>
+      <x:c r="J42" s="334" t="str"/>
+      <x:c r="K42" s="334" t="str"/>
+      <x:c r="L42" s="334" t="str"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="334" t="str"/>
+      <x:c r="B43" s="334" t="str"/>
+      <x:c r="C43" s="334" t="str"/>
+      <x:c r="D43" s="334" t="str"/>
+      <x:c r="E43" s="334" t="str"/>
+      <x:c r="F43" s="334" t="str"/>
+      <x:c r="G43" s="334" t="str"/>
+      <x:c r="H43" s="334" t="str"/>
+      <x:c r="I43" s="334" t="str"/>
+      <x:c r="J43" s="334" t="str"/>
+      <x:c r="K43" s="334" t="str"/>
+      <x:c r="L43" s="334" t="str"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="334" t="str"/>
+      <x:c r="B44" s="334" t="str"/>
+      <x:c r="C44" s="334" t="str"/>
+      <x:c r="D44" s="334" t="str"/>
+      <x:c r="E44" s="334" t="str"/>
+      <x:c r="F44" s="334" t="str"/>
+      <x:c r="G44" s="334" t="str"/>
+      <x:c r="H44" s="334" t="str"/>
+      <x:c r="I44" s="334" t="str"/>
+      <x:c r="J44" s="334" t="str"/>
+      <x:c r="K44" s="334" t="str"/>
+      <x:c r="L44" s="334" t="str"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="334" t="str"/>
+      <x:c r="B45" s="334" t="str"/>
+      <x:c r="C45" s="334" t="str"/>
+      <x:c r="D45" s="334" t="str"/>
+      <x:c r="E45" s="334" t="str"/>
+      <x:c r="F45" s="334" t="str"/>
+      <x:c r="G45" s="334" t="str"/>
+      <x:c r="H45" s="334" t="str"/>
+      <x:c r="I45" s="334" t="str"/>
+      <x:c r="J45" s="334" t="str"/>
+      <x:c r="K45" s="334" t="str"/>
+      <x:c r="L45" s="334" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:L2"/>
+    <x:mergeCell ref="A3:B3"/>
+    <x:mergeCell ref="C3:H3"/>
+    <x:mergeCell ref="I3:J3"/>
+    <x:mergeCell ref="K3:L3"/>
+    <x:mergeCell ref="A4:B4"/>
+    <x:mergeCell ref="C4:H4"/>
+    <x:mergeCell ref="I4:J4"/>
+    <x:mergeCell ref="K4:L4"/>
+    <x:mergeCell ref="A5:B5"/>
+    <x:mergeCell ref="C5:H5"/>
+    <x:mergeCell ref="I5:J5"/>
+    <x:mergeCell ref="K5:L5"/>
+    <x:mergeCell ref="A7:L7"/>
+    <x:mergeCell ref="A37:L37"/>
+    <x:mergeCell ref="A38:L45"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>